--- a/TABELÃO_v1.0.xlsx
+++ b/TABELÃO_v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tabelao-bu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124109BD-F6B8-424B-9CBD-7E9B58610129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEA0630-5327-4621-90B6-A08048105778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="327" xr2:uid="{06165158-AD63-4570-8E55-AFED79D91195}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="327" activeTab="2" xr2:uid="{06165158-AD63-4570-8E55-AFED79D91195}"/>
   </bookViews>
   <sheets>
     <sheet name="Imoveis" sheetId="16" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="Veiculos" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Carbuy!$B$2:$U$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Imoveis!$B$2:$U$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Carbuy!$B$2:$U$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Imoveis!$B$2:$U$29</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="33">
   <si>
     <t>Negócio</t>
   </si>
@@ -89,9 +89,6 @@
     <t>Dia</t>
   </si>
   <si>
-    <t>Jan</t>
-  </si>
-  <si>
     <t>Clique</t>
   </si>
   <si>
@@ -99,9 +96,6 @@
   </si>
   <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>JAN</t>
   </si>
   <si>
     <t>Faturamento</t>
@@ -156,7 +150,7 @@
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$-416]d\-mmm;@"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -269,7 +263,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -314,11 +308,11 @@
     <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
@@ -341,10 +335,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -377,9 +367,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>896303</xdr:colOff>
+      <xdr:colOff>892493</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>20002</xdr:rowOff>
+      <xdr:rowOff>16192</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -511,7 +501,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>724500</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>57838</xdr:rowOff>
+      <xdr:rowOff>54028</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -585,9 +575,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>782112</xdr:colOff>
+      <xdr:colOff>778302</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>94995</xdr:rowOff>
+      <xdr:rowOff>98805</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -727,9 +717,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>781368</xdr:colOff>
+      <xdr:colOff>777558</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>91714</xdr:rowOff>
+      <xdr:rowOff>95524</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -806,9 +796,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>896303</xdr:colOff>
+      <xdr:colOff>892493</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>20002</xdr:rowOff>
+      <xdr:rowOff>16192</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1008,7 +998,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>724145</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>9773</xdr:rowOff>
+      <xdr:rowOff>19298</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1082,9 +1072,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>778302</xdr:colOff>
+      <xdr:colOff>782112</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>102615</xdr:rowOff>
+      <xdr:rowOff>98805</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1156,9 +1146,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>781368</xdr:colOff>
+      <xdr:colOff>777558</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>84094</xdr:rowOff>
+      <xdr:rowOff>91714</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1235,9 +1225,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>892493</xdr:colOff>
+      <xdr:colOff>896303</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>20434</xdr:rowOff>
+      <xdr:rowOff>16624</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1437,7 +1427,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>724500</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>60803</xdr:rowOff>
+      <xdr:rowOff>56993</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1585,9 +1575,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>777558</xdr:colOff>
+      <xdr:colOff>781368</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>99043</xdr:rowOff>
+      <xdr:rowOff>95233</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1973,7 +1963,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="B1:V1048572"/>
+  <dimension ref="B1:V1048571"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" customWidth="1"/>
@@ -2048,40 +2038,40 @@
         <v>5</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" s="18" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L2" s="18" t="s">
         <v>7</v>
       </c>
       <c r="M2" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="P2" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" s="18" t="s">
-        <v>24</v>
-      </c>
       <c r="R2" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S2" s="18" t="s">
         <v>8</v>
@@ -2098,7 +2088,7 @@
         <v>46023</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" s="7">
         <v>0</v>
@@ -2159,7 +2149,7 @@
         <v>46024</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="7">
         <v>0</v>
@@ -2222,7 +2212,7 @@
         <v>46025</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" s="11">
         <v>0</v>
@@ -2285,7 +2275,7 @@
         <v>46027</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" s="7">
         <v>0</v>
@@ -2348,25 +2338,25 @@
         <v>46028</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="7">
         <v>0</v>
       </c>
       <c r="F7" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="9">
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H7" s="8">
-        <v>2627400</v>
+        <v>2764844.75</v>
       </c>
       <c r="I7" s="8">
-        <v>0</v>
+        <v>305444.75</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>13</v>
@@ -2411,7 +2401,7 @@
         <v>46029</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" s="7">
         <v>0</v>
@@ -2474,25 +2464,25 @@
         <v>46030</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D9" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" s="9">
-        <v>0</v>
+        <v>7.1428571428571425E-2</v>
       </c>
       <c r="H9" s="8">
-        <v>20214604.57</v>
+        <v>20264604.57</v>
       </c>
       <c r="I9" s="8">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
@@ -2537,7 +2527,7 @@
         <v>46031</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D10" s="7">
         <v>1</v>
@@ -2600,7 +2590,7 @@
         <v>46032</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D11" s="11">
         <v>0</v>
@@ -2663,25 +2653,25 @@
         <v>46034</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D12" s="7">
+        <v>16</v>
+      </c>
+      <c r="E12" s="7">
         <v>2</v>
       </c>
-      <c r="E12" s="7">
-        <v>0</v>
-      </c>
       <c r="F12" s="7">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="G12" s="9">
-        <v>0.18181818181818182</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="H12" s="8">
-        <v>3793000</v>
+        <v>6445000</v>
       </c>
       <c r="I12" s="8">
-        <v>532000</v>
+        <v>4557000</v>
       </c>
       <c r="J12" s="7">
         <v>2</v>
@@ -2726,13 +2716,13 @@
         <v>46035</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D13" s="7">
         <v>0</v>
       </c>
       <c r="E13" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="7">
         <v>0</v>
@@ -2789,7 +2779,7 @@
         <v>46036</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" s="7">
         <v>0</v>
@@ -2852,7 +2842,7 @@
         <v>46037</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15" s="7">
         <v>0</v>
@@ -2915,25 +2905,25 @@
         <v>46038</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="7">
         <v>0</v>
       </c>
       <c r="F16" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G16" s="9">
-        <v>0.14285714285714285</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H16" s="8">
-        <v>1874773.63</v>
+        <v>2310794.09</v>
       </c>
       <c r="I16" s="8">
-        <v>80342.59</v>
+        <v>413473.13</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>13</v>
@@ -2978,7 +2968,7 @@
         <v>46039</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D17" s="11">
         <v>0</v>
@@ -3005,13 +2995,13 @@
         <v>13</v>
       </c>
       <c r="L17" s="11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M17" s="11">
         <v>67</v>
       </c>
       <c r="N17" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O17" s="11">
         <v>0</v>
@@ -3029,7 +3019,7 @@
         <v>1159922</v>
       </c>
       <c r="T17" s="20">
-        <v>140.62</v>
+        <v>140.61999999999998</v>
       </c>
       <c r="U17" s="12">
         <v>1.0275690951632955E-2</v>
@@ -3041,25 +3031,25 @@
         <v>46041</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D18" s="7">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="E18" s="7">
         <v>0</v>
       </c>
       <c r="F18" s="7">
-        <v>337</v>
+        <v>442</v>
       </c>
       <c r="G18" s="9">
-        <v>7.418397626112759E-2</v>
+        <v>0.27828054298642535</v>
       </c>
       <c r="H18" s="8">
-        <v>45592478.760000005</v>
+        <v>59081003.550000019</v>
       </c>
       <c r="I18" s="8">
-        <v>5677723.7399999993</v>
+        <v>20742835.069999993</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>13</v>
@@ -3071,10 +3061,10 @@
         <v>25</v>
       </c>
       <c r="M18" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N18" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O18" s="7">
         <v>0</v>
@@ -3092,7 +3082,7 @@
         <v>878024</v>
       </c>
       <c r="T18" s="19">
-        <v>227.69000000000003</v>
+        <v>227.68999999999994</v>
       </c>
       <c r="U18" s="9">
         <v>8.3152624529625619E-3</v>
@@ -3104,25 +3094,25 @@
         <v>46042</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D19" s="7">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E19" s="7">
         <v>0</v>
       </c>
       <c r="F19" s="7">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G19" s="9">
-        <v>0.15789473684210525</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H19" s="8">
-        <v>13391562.369999999</v>
+        <v>15520562.369999999</v>
       </c>
       <c r="I19" s="8">
-        <v>1287000</v>
+        <v>3313000</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>13</v>
@@ -3167,7 +3157,7 @@
         <v>46043</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D20" s="7">
         <v>0</v>
@@ -3230,7 +3220,7 @@
         <v>46044</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D21" s="7">
         <v>0</v>
@@ -3293,37 +3283,37 @@
         <v>46045</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D22" s="11">
         <v>0</v>
       </c>
       <c r="E22" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G22" s="12">
         <v>0</v>
       </c>
       <c r="H22" s="13">
-        <v>2581928.7599999998</v>
+        <v>3091928.76</v>
       </c>
       <c r="I22" s="13">
         <v>0</v>
       </c>
-      <c r="J22" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>13</v>
+      <c r="J22" s="11">
+        <v>1</v>
+      </c>
+      <c r="K22" s="11">
+        <v>1</v>
       </c>
       <c r="L22" s="11">
         <v>98</v>
       </c>
       <c r="M22" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N22" s="11">
         <v>18</v>
@@ -3356,7 +3346,7 @@
         <v>46046</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D23" s="11">
         <v>0</v>
@@ -3407,7 +3397,7 @@
         <v>601754</v>
       </c>
       <c r="T23" s="20">
-        <v>76.499999999999986</v>
+        <v>76.499999999999972</v>
       </c>
       <c r="U23" s="12">
         <v>1.0404583932969287E-2</v>
@@ -3419,13 +3409,13 @@
         <v>46048</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D24" s="7">
         <v>0</v>
       </c>
       <c r="E24" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="7">
         <v>0</v>
@@ -3439,17 +3429,17 @@
       <c r="I24" s="8">
         <v>0</v>
       </c>
-      <c r="J24" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>13</v>
+      <c r="J24" s="7">
+        <v>1</v>
+      </c>
+      <c r="K24" s="7">
+        <v>1</v>
       </c>
       <c r="L24" s="7">
         <v>61</v>
       </c>
       <c r="M24" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N24" s="7">
         <v>34</v>
@@ -3470,7 +3460,7 @@
         <v>744182</v>
       </c>
       <c r="T24" s="19">
-        <v>81.730000000000061</v>
+        <v>81.730000000000032</v>
       </c>
       <c r="U24" s="9">
         <v>9.5863646258576539E-3</v>
@@ -3482,13 +3472,13 @@
         <v>46049</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D25" s="7">
         <v>0</v>
       </c>
       <c r="E25" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" s="7">
         <v>3</v>
@@ -3502,11 +3492,11 @@
       <c r="I25" s="8">
         <v>0</v>
       </c>
-      <c r="J25" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>13</v>
+      <c r="J25" s="7">
+        <v>2</v>
+      </c>
+      <c r="K25" s="7">
+        <v>2</v>
       </c>
       <c r="L25" s="7">
         <v>85</v>
@@ -3533,7 +3523,7 @@
         <v>726677</v>
       </c>
       <c r="T25" s="19">
-        <v>88.4</v>
+        <v>88.399999999999991</v>
       </c>
       <c r="U25" s="9">
         <v>9.6136247603818472E-3</v>
@@ -3545,31 +3535,31 @@
         <v>46050</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D26" s="7">
         <v>0</v>
       </c>
       <c r="E26" s="7">
+        <v>4</v>
+      </c>
+      <c r="F26" s="7">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="8">
+        <v>0</v>
+      </c>
+      <c r="I26" s="8">
+        <v>0</v>
+      </c>
+      <c r="J26" s="7">
         <v>2</v>
       </c>
-      <c r="F26" s="7">
-        <v>0</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="8">
-        <v>0</v>
-      </c>
-      <c r="I26" s="8">
-        <v>0</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>13</v>
+      <c r="K26" s="7">
+        <v>2</v>
       </c>
       <c r="L26" s="7">
         <v>57</v>
@@ -3608,31 +3598,31 @@
         <v>46051</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D27" s="7">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E27" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" s="7">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="G27" s="9">
-        <v>0.06</v>
+        <v>0.2537313432835821</v>
       </c>
       <c r="H27" s="8">
-        <v>46611418.489999995</v>
+        <v>49418016.569999993</v>
       </c>
       <c r="I27" s="8">
-        <v>499000</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>13</v>
+        <v>3095874.73</v>
+      </c>
+      <c r="J27" s="7">
+        <v>1</v>
+      </c>
+      <c r="K27" s="7">
+        <v>1</v>
       </c>
       <c r="L27" s="7">
         <v>39</v>
@@ -3671,10 +3661,10 @@
         <v>46052</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D28" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="7">
         <v>0</v>
@@ -3683,13 +3673,13 @@
         <v>25</v>
       </c>
       <c r="G28" s="9">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H28" s="8">
-        <v>68525441.169999987</v>
+        <v>62398615.009999998</v>
       </c>
       <c r="I28" s="8">
-        <v>201000</v>
+        <v>384540.17000000004</v>
       </c>
       <c r="J28" s="7" t="s">
         <v>13</v>
@@ -3722,7 +3712,7 @@
         <v>326037</v>
       </c>
       <c r="T28" s="19">
-        <v>132.61000000000004</v>
+        <v>132.61000000000001</v>
       </c>
       <c r="U28" s="9">
         <v>8.8026819042010575E-3</v>
@@ -3734,7 +3724,7 @@
         <v>46053</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D29" s="11">
         <v>0</v>
@@ -3793,116 +3783,1532 @@
       <c r="V29" s="2"/>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="6">
+        <v>46055</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="7">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7">
+        <v>2</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="8">
+        <v>1707107.7</v>
+      </c>
+      <c r="I30" s="8">
+        <v>0</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L30" s="7">
+        <v>6</v>
+      </c>
+      <c r="M30" s="7">
+        <v>23</v>
+      </c>
+      <c r="N30" s="7">
         <v>19</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="11">
-        <v>36</v>
-      </c>
-      <c r="E30" s="11">
+      <c r="O30" s="7">
+        <v>0</v>
+      </c>
+      <c r="P30" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="7">
+        <v>0</v>
+      </c>
+      <c r="R30" s="7">
+        <v>4184</v>
+      </c>
+      <c r="S30" s="7">
+        <v>433524</v>
+      </c>
+      <c r="T30" s="19">
+        <v>45.86</v>
+      </c>
+      <c r="U30" s="9">
+        <v>9.6511381146141845E-3</v>
+      </c>
+      <c r="V30" s="2"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B31" s="6">
+        <v>46056</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="7">
+        <v>0</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7">
+        <v>1</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>750000</v>
+      </c>
+      <c r="I31" s="8">
+        <v>0</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L31" s="7">
+        <v>14</v>
+      </c>
+      <c r="M31" s="7">
+        <v>30</v>
+      </c>
+      <c r="N31" s="7">
+        <v>21</v>
+      </c>
+      <c r="O31" s="7">
+        <v>0</v>
+      </c>
+      <c r="P31" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="7">
+        <v>0</v>
+      </c>
+      <c r="R31" s="7">
+        <v>3799</v>
+      </c>
+      <c r="S31" s="7">
+        <v>435334</v>
+      </c>
+      <c r="T31" s="19">
+        <v>85.139999999999986</v>
+      </c>
+      <c r="U31" s="9">
+        <v>8.7266328841762875E-3</v>
+      </c>
+      <c r="V31" s="2"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B32" s="6">
+        <v>46057</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="7">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="8">
+        <v>0</v>
+      </c>
+      <c r="I32" s="8">
+        <v>0</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L32" s="7">
+        <v>57</v>
+      </c>
+      <c r="M32" s="7">
+        <v>24</v>
+      </c>
+      <c r="N32" s="7">
+        <v>16</v>
+      </c>
+      <c r="O32" s="7">
+        <v>0</v>
+      </c>
+      <c r="P32" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="7">
+        <v>0</v>
+      </c>
+      <c r="R32" s="7">
+        <v>5094</v>
+      </c>
+      <c r="S32" s="7">
+        <v>545747</v>
+      </c>
+      <c r="T32" s="19">
+        <v>80.98</v>
+      </c>
+      <c r="U32" s="9">
+        <v>9.3339954227874816E-3</v>
+      </c>
+      <c r="V32" s="2"/>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B33" s="6">
+        <v>46058</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="7">
+        <v>1</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0</v>
+      </c>
+      <c r="F33" s="7">
+        <v>11</v>
+      </c>
+      <c r="G33" s="9">
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="H33" s="8">
+        <v>5401594.5</v>
+      </c>
+      <c r="I33" s="8">
+        <v>110469.52</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L33" s="7">
+        <v>11</v>
+      </c>
+      <c r="M33" s="7">
+        <v>31</v>
+      </c>
+      <c r="N33" s="7">
+        <v>30</v>
+      </c>
+      <c r="O33" s="7">
+        <v>0</v>
+      </c>
+      <c r="P33" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="7">
+        <v>0</v>
+      </c>
+      <c r="R33" s="7">
+        <v>4857</v>
+      </c>
+      <c r="S33" s="7">
+        <v>541926</v>
+      </c>
+      <c r="T33" s="19">
+        <v>89.119999999999976</v>
+      </c>
+      <c r="U33" s="9">
+        <v>8.9624782719411877E-3</v>
+      </c>
+      <c r="V33" s="2"/>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B34" s="6">
+        <v>46059</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="7">
+        <v>10</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7">
+        <v>29</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0.34482758620689657</v>
+      </c>
+      <c r="H34" s="8">
+        <v>17446483.270000003</v>
+      </c>
+      <c r="I34" s="8">
+        <v>3103576.5</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L34" s="7">
+        <v>32</v>
+      </c>
+      <c r="M34" s="7">
+        <v>15</v>
+      </c>
+      <c r="N34" s="7">
+        <v>12</v>
+      </c>
+      <c r="O34" s="7">
+        <v>0</v>
+      </c>
+      <c r="P34" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="7">
+        <v>0</v>
+      </c>
+      <c r="R34" s="7">
+        <v>3187</v>
+      </c>
+      <c r="S34" s="7">
+        <v>367974</v>
+      </c>
+      <c r="T34" s="19">
+        <v>141.03000000000006</v>
+      </c>
+      <c r="U34" s="9">
+        <v>8.6609380010544221E-3</v>
+      </c>
+      <c r="V34" s="2"/>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B35" s="10">
+        <v>46060</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="11">
+        <v>0</v>
+      </c>
+      <c r="E35" s="11">
+        <v>0</v>
+      </c>
+      <c r="F35" s="11">
+        <v>0</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="13">
+        <v>0</v>
+      </c>
+      <c r="I35" s="13">
+        <v>0</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="L35" s="11">
+        <v>62</v>
+      </c>
+      <c r="M35" s="11">
+        <v>12</v>
+      </c>
+      <c r="N35" s="11">
+        <v>9</v>
+      </c>
+      <c r="O35" s="11">
+        <v>0</v>
+      </c>
+      <c r="P35" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="11">
+        <v>0</v>
+      </c>
+      <c r="R35" s="11">
+        <v>2697</v>
+      </c>
+      <c r="S35" s="11">
+        <v>303198</v>
+      </c>
+      <c r="T35" s="20">
+        <v>61.290000000000006</v>
+      </c>
+      <c r="U35" s="12">
+        <v>8.8951774088219578E-3</v>
+      </c>
+      <c r="V35" s="2"/>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B36" s="6">
+        <v>46062</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="7">
+        <v>1</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7">
+        <v>6</v>
+      </c>
+      <c r="G36" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H36" s="8">
+        <v>7223180.8399999999</v>
+      </c>
+      <c r="I36" s="8">
+        <v>197622.71</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L36" s="7">
+        <v>32</v>
+      </c>
+      <c r="M36" s="7">
+        <v>28</v>
+      </c>
+      <c r="N36" s="7">
+        <v>21</v>
+      </c>
+      <c r="O36" s="7">
+        <v>0</v>
+      </c>
+      <c r="P36" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="7">
+        <v>0</v>
+      </c>
+      <c r="R36" s="7">
+        <v>3044</v>
+      </c>
+      <c r="S36" s="7">
+        <v>369834</v>
+      </c>
+      <c r="T36" s="19">
+        <v>56.179999999999993</v>
+      </c>
+      <c r="U36" s="9">
+        <v>8.2307197283105395E-3</v>
+      </c>
+      <c r="V36" s="2"/>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B37" s="6">
+        <v>46063</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" s="7">
+        <v>0</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0</v>
+      </c>
+      <c r="F37" s="7">
         <v>3</v>
       </c>
-      <c r="F30" s="11">
-        <v>509</v>
-      </c>
-      <c r="G30" s="12">
-        <v>7.072691552062868E-2</v>
-      </c>
-      <c r="H30" s="13">
-        <v>279937048.02999997</v>
-      </c>
-      <c r="I30" s="13">
-        <v>8416473.3299999982</v>
-      </c>
-      <c r="J30" s="11">
-        <v>7</v>
-      </c>
-      <c r="K30" s="11">
-        <v>5</v>
-      </c>
-      <c r="L30" s="11">
-        <v>1063</v>
-      </c>
-      <c r="M30" s="11">
-        <v>1331</v>
-      </c>
-      <c r="N30" s="11">
-        <v>1106</v>
-      </c>
-      <c r="O30" s="11">
-        <v>0</v>
-      </c>
-      <c r="P30" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="11">
-        <v>0</v>
-      </c>
-      <c r="R30" s="11">
-        <v>145182</v>
-      </c>
-      <c r="S30" s="11">
-        <v>15476027</v>
-      </c>
-      <c r="T30" s="20">
-        <v>2401.2600000000002</v>
-      </c>
-      <c r="U30" s="12">
-        <v>0.24639767615371108</v>
-      </c>
-      <c r="V30" s="2"/>
-    </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="V31" s="2"/>
-    </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="V32" s="2"/>
-    </row>
-    <row r="33" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V33" s="2"/>
-    </row>
-    <row r="34" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V34" s="2"/>
-    </row>
-    <row r="35" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V35" s="2"/>
-    </row>
-    <row r="36" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V36" s="2"/>
-    </row>
-    <row r="37" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="G37" s="9">
+        <v>0</v>
+      </c>
+      <c r="H37" s="8">
+        <v>333000</v>
+      </c>
+      <c r="I37" s="8">
+        <v>0</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L37" s="7">
+        <v>25</v>
+      </c>
+      <c r="M37" s="7">
+        <v>21</v>
+      </c>
+      <c r="N37" s="7">
+        <v>15</v>
+      </c>
+      <c r="O37" s="7">
+        <v>0</v>
+      </c>
+      <c r="P37" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="7">
+        <v>0</v>
+      </c>
+      <c r="R37" s="7">
+        <v>2774</v>
+      </c>
+      <c r="S37" s="7">
+        <v>342295</v>
+      </c>
+      <c r="T37" s="19">
+        <v>74.8</v>
+      </c>
+      <c r="U37" s="9">
+        <v>8.1041207145882942E-3</v>
+      </c>
       <c r="V37" s="2"/>
     </row>
-    <row r="38" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B38" s="6">
+        <v>46064</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="7">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="8">
+        <v>0</v>
+      </c>
+      <c r="I38" s="8">
+        <v>0</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L38" s="7">
+        <v>33</v>
+      </c>
+      <c r="M38" s="7">
+        <v>22</v>
+      </c>
+      <c r="N38" s="7">
+        <v>17</v>
+      </c>
+      <c r="O38" s="7">
+        <v>0</v>
+      </c>
+      <c r="P38" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="7">
+        <v>0</v>
+      </c>
+      <c r="R38" s="7">
+        <v>3628</v>
+      </c>
+      <c r="S38" s="7">
+        <v>449234</v>
+      </c>
+      <c r="T38" s="19">
+        <v>62.759999999999991</v>
+      </c>
+      <c r="U38" s="9">
+        <v>8.0759693166590242E-3</v>
+      </c>
       <c r="V38" s="2"/>
     </row>
-    <row r="39" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B39" s="6">
+        <v>46065</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="7">
+        <v>0</v>
+      </c>
+      <c r="E39" s="7">
+        <v>1</v>
+      </c>
+      <c r="F39" s="7">
+        <v>20</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0</v>
+      </c>
+      <c r="H39" s="8">
+        <v>31133860.18</v>
+      </c>
+      <c r="I39" s="8">
+        <v>0</v>
+      </c>
+      <c r="J39" s="7">
+        <v>1</v>
+      </c>
+      <c r="K39" s="7">
+        <v>1</v>
+      </c>
+      <c r="L39" s="7">
+        <v>56</v>
+      </c>
+      <c r="M39" s="7">
+        <v>14</v>
+      </c>
+      <c r="N39" s="7">
+        <v>14</v>
+      </c>
+      <c r="O39" s="7">
+        <v>0</v>
+      </c>
+      <c r="P39" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="7">
+        <v>0</v>
+      </c>
+      <c r="R39" s="7">
+        <v>0</v>
+      </c>
+      <c r="S39" s="7">
+        <v>0</v>
+      </c>
+      <c r="T39" s="19">
+        <v>0</v>
+      </c>
+      <c r="U39" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="V39" s="2"/>
     </row>
-    <row r="40" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B40" s="6">
+        <v>46066</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7">
+        <v>14</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="8">
+        <v>6169621.1099999994</v>
+      </c>
+      <c r="I40" s="8">
+        <v>0</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L40" s="7">
+        <v>9</v>
+      </c>
+      <c r="M40" s="7">
+        <v>0</v>
+      </c>
+      <c r="N40" s="7">
+        <v>0</v>
+      </c>
+      <c r="O40" s="7">
+        <v>0</v>
+      </c>
+      <c r="P40" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="7">
+        <v>0</v>
+      </c>
+      <c r="R40" s="7">
+        <v>0</v>
+      </c>
+      <c r="S40" s="7">
+        <v>0</v>
+      </c>
+      <c r="T40" s="19">
+        <v>0</v>
+      </c>
+      <c r="U40" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="V40" s="2"/>
     </row>
-    <row r="41" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B41" s="10">
+        <v>46067</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="11">
+        <v>0</v>
+      </c>
+      <c r="E41" s="11">
+        <v>0</v>
+      </c>
+      <c r="F41" s="11">
+        <v>0</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="13">
+        <v>0</v>
+      </c>
+      <c r="I41" s="13">
+        <v>0</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="L41" s="11">
+        <v>0</v>
+      </c>
+      <c r="M41" s="11">
+        <v>0</v>
+      </c>
+      <c r="N41" s="11">
+        <v>0</v>
+      </c>
+      <c r="O41" s="11">
+        <v>0</v>
+      </c>
+      <c r="P41" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="11">
+        <v>0</v>
+      </c>
+      <c r="R41" s="11">
+        <v>0</v>
+      </c>
+      <c r="S41" s="11">
+        <v>0</v>
+      </c>
+      <c r="T41" s="20">
+        <v>0</v>
+      </c>
+      <c r="U41" s="12" t="s">
+        <v>12</v>
+      </c>
       <c r="V41" s="2"/>
     </row>
-    <row r="42" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V42" s="2"/>
-    </row>
-    <row r="1048572" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G1048572" s="3">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B42" s="6">
+        <v>46069</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="7">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7">
+        <v>0</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="8">
+        <v>0</v>
+      </c>
+      <c r="I42" s="8">
+        <v>0</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L42" s="7">
+        <v>0</v>
+      </c>
+      <c r="M42" s="7">
+        <v>0</v>
+      </c>
+      <c r="N42" s="7">
+        <v>0</v>
+      </c>
+      <c r="O42" s="7">
+        <v>0</v>
+      </c>
+      <c r="P42" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="7">
+        <v>0</v>
+      </c>
+      <c r="R42" s="7">
+        <v>0</v>
+      </c>
+      <c r="S42" s="7">
+        <v>0</v>
+      </c>
+      <c r="T42" s="19">
+        <v>0</v>
+      </c>
+      <c r="U42" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B43" s="6">
+        <v>46070</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" s="7">
+        <v>0</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0</v>
+      </c>
+      <c r="F43" s="7">
+        <v>0</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="8">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8">
+        <v>0</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L43" s="7">
+        <v>0</v>
+      </c>
+      <c r="M43" s="7">
+        <v>0</v>
+      </c>
+      <c r="N43" s="7">
+        <v>0</v>
+      </c>
+      <c r="O43" s="7">
+        <v>0</v>
+      </c>
+      <c r="P43" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="7">
+        <v>0</v>
+      </c>
+      <c r="R43" s="7">
+        <v>0</v>
+      </c>
+      <c r="S43" s="7">
+        <v>0</v>
+      </c>
+      <c r="T43" s="19">
+        <v>0</v>
+      </c>
+      <c r="U43" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B44" s="6">
+        <v>46071</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="7">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7">
+        <v>11</v>
+      </c>
+      <c r="G44" s="9">
+        <v>0</v>
+      </c>
+      <c r="H44" s="8">
+        <v>4398438.53</v>
+      </c>
+      <c r="I44" s="8">
+        <v>0</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L44" s="7">
+        <v>0</v>
+      </c>
+      <c r="M44" s="7">
+        <v>0</v>
+      </c>
+      <c r="N44" s="7">
+        <v>0</v>
+      </c>
+      <c r="O44" s="7">
+        <v>0</v>
+      </c>
+      <c r="P44" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="7">
+        <v>0</v>
+      </c>
+      <c r="R44" s="7">
+        <v>0</v>
+      </c>
+      <c r="S44" s="7">
+        <v>0</v>
+      </c>
+      <c r="T44" s="19">
+        <v>0</v>
+      </c>
+      <c r="U44" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B45" s="6">
+        <v>46072</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="7">
+        <v>0</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0</v>
+      </c>
+      <c r="F45" s="7">
+        <v>0</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" s="8">
+        <v>0</v>
+      </c>
+      <c r="I45" s="8">
+        <v>0</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L45" s="7">
+        <v>0</v>
+      </c>
+      <c r="M45" s="7">
+        <v>0</v>
+      </c>
+      <c r="N45" s="7">
+        <v>0</v>
+      </c>
+      <c r="O45" s="7">
+        <v>0</v>
+      </c>
+      <c r="P45" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="7">
+        <v>0</v>
+      </c>
+      <c r="R45" s="7">
+        <v>0</v>
+      </c>
+      <c r="S45" s="7">
+        <v>0</v>
+      </c>
+      <c r="T45" s="19">
+        <v>0</v>
+      </c>
+      <c r="U45" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B46" s="6">
+        <v>46073</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7">
+        <v>1</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="8">
+        <v>9000</v>
+      </c>
+      <c r="I46" s="8">
+        <v>0</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L46" s="7">
+        <v>3</v>
+      </c>
+      <c r="M46" s="7">
+        <v>0</v>
+      </c>
+      <c r="N46" s="7">
+        <v>0</v>
+      </c>
+      <c r="O46" s="7">
+        <v>0</v>
+      </c>
+      <c r="P46" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="7">
+        <v>0</v>
+      </c>
+      <c r="R46" s="7">
+        <v>0</v>
+      </c>
+      <c r="S46" s="7">
+        <v>0</v>
+      </c>
+      <c r="T46" s="19">
+        <v>0</v>
+      </c>
+      <c r="U46" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B47" s="10">
+        <v>46074</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="11">
+        <v>0</v>
+      </c>
+      <c r="E47" s="11">
+        <v>0</v>
+      </c>
+      <c r="F47" s="11">
+        <v>0</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" s="13">
+        <v>0</v>
+      </c>
+      <c r="I47" s="13">
+        <v>0</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="L47" s="11">
+        <v>0</v>
+      </c>
+      <c r="M47" s="11">
+        <v>0</v>
+      </c>
+      <c r="N47" s="11">
+        <v>0</v>
+      </c>
+      <c r="O47" s="11">
+        <v>0</v>
+      </c>
+      <c r="P47" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="11">
+        <v>0</v>
+      </c>
+      <c r="R47" s="11">
+        <v>0</v>
+      </c>
+      <c r="S47" s="11">
+        <v>0</v>
+      </c>
+      <c r="T47" s="20">
+        <v>0</v>
+      </c>
+      <c r="U47" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B48" s="6">
+        <v>46076</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="7">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7">
+        <v>9</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0</v>
+      </c>
+      <c r="H48" s="8">
+        <v>11258730.01</v>
+      </c>
+      <c r="I48" s="8">
+        <v>0</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L48" s="7">
+        <v>0</v>
+      </c>
+      <c r="M48" s="7">
+        <v>0</v>
+      </c>
+      <c r="N48" s="7">
+        <v>0</v>
+      </c>
+      <c r="O48" s="7">
+        <v>0</v>
+      </c>
+      <c r="P48" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="7">
+        <v>0</v>
+      </c>
+      <c r="R48" s="7">
+        <v>0</v>
+      </c>
+      <c r="S48" s="7">
+        <v>0</v>
+      </c>
+      <c r="T48" s="19">
+        <v>0</v>
+      </c>
+      <c r="U48" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B49" s="6">
+        <v>46077</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" s="7">
+        <v>0</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0</v>
+      </c>
+      <c r="F49" s="7">
+        <v>1</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0</v>
+      </c>
+      <c r="H49" s="8">
+        <v>3480000</v>
+      </c>
+      <c r="I49" s="8">
+        <v>0</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L49" s="7">
+        <v>2</v>
+      </c>
+      <c r="M49" s="7">
+        <v>0</v>
+      </c>
+      <c r="N49" s="7">
+        <v>0</v>
+      </c>
+      <c r="O49" s="7">
+        <v>0</v>
+      </c>
+      <c r="P49" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="7">
+        <v>0</v>
+      </c>
+      <c r="R49" s="7">
+        <v>0</v>
+      </c>
+      <c r="S49" s="7">
+        <v>0</v>
+      </c>
+      <c r="T49" s="19">
+        <v>0</v>
+      </c>
+      <c r="U49" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B50" s="6">
+        <v>46078</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" s="7">
+        <v>0</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7">
+        <v>29</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="8">
+        <v>17506033.66</v>
+      </c>
+      <c r="I50" s="8">
+        <v>0</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L50" s="7">
+        <v>0</v>
+      </c>
+      <c r="M50" s="7">
+        <v>0</v>
+      </c>
+      <c r="N50" s="7">
+        <v>0</v>
+      </c>
+      <c r="O50" s="7">
+        <v>0</v>
+      </c>
+      <c r="P50" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="7">
+        <v>0</v>
+      </c>
+      <c r="R50" s="7">
+        <v>0</v>
+      </c>
+      <c r="S50" s="7">
+        <v>0</v>
+      </c>
+      <c r="T50" s="19">
+        <v>0</v>
+      </c>
+      <c r="U50" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B51" s="6">
+        <v>46079</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" s="7">
+        <v>0</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0</v>
+      </c>
+      <c r="F51" s="7">
+        <v>19</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0</v>
+      </c>
+      <c r="H51" s="8">
+        <v>42372645.600000001</v>
+      </c>
+      <c r="I51" s="8">
+        <v>0</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L51" s="7">
+        <v>0</v>
+      </c>
+      <c r="M51" s="7">
+        <v>0</v>
+      </c>
+      <c r="N51" s="7">
+        <v>0</v>
+      </c>
+      <c r="O51" s="7">
+        <v>0</v>
+      </c>
+      <c r="P51" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="7">
+        <v>0</v>
+      </c>
+      <c r="R51" s="7">
+        <v>0</v>
+      </c>
+      <c r="S51" s="7">
+        <v>0</v>
+      </c>
+      <c r="T51" s="19">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B52" s="6">
+        <v>46080</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" s="7">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7">
+        <v>24</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="8">
+        <v>48065750</v>
+      </c>
+      <c r="I52" s="8">
+        <v>0</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L52" s="7">
+        <v>4</v>
+      </c>
+      <c r="M52" s="7">
+        <v>0</v>
+      </c>
+      <c r="N52" s="7">
+        <v>0</v>
+      </c>
+      <c r="O52" s="7">
+        <v>0</v>
+      </c>
+      <c r="P52" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="7">
+        <v>0</v>
+      </c>
+      <c r="R52" s="7">
+        <v>0</v>
+      </c>
+      <c r="S52" s="7">
+        <v>0</v>
+      </c>
+      <c r="T52" s="19">
+        <v>0</v>
+      </c>
+      <c r="U52" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B53" s="10">
+        <v>46081</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" s="11">
+        <v>0</v>
+      </c>
+      <c r="E53" s="11">
+        <v>0</v>
+      </c>
+      <c r="F53" s="11">
+        <v>0</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" s="13">
+        <v>0</v>
+      </c>
+      <c r="I53" s="13">
+        <v>0</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="L53" s="11">
+        <v>0</v>
+      </c>
+      <c r="M53" s="11">
+        <v>0</v>
+      </c>
+      <c r="N53" s="11">
+        <v>0</v>
+      </c>
+      <c r="O53" s="11">
+        <v>0</v>
+      </c>
+      <c r="P53" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="11">
+        <v>0</v>
+      </c>
+      <c r="R53" s="11">
+        <v>0</v>
+      </c>
+      <c r="S53" s="11">
+        <v>0</v>
+      </c>
+      <c r="T53" s="20">
+        <v>0</v>
+      </c>
+      <c r="U53" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1048571" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G1048571" s="3">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="R1:U1"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
-  <conditionalFormatting sqref="G3:G1048576">
+  <conditionalFormatting sqref="G54:G1048576">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{27EC871F-0598-464F-9811-19D6BE4C535C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G53">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -3911,7 +5317,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{27EC871F-0598-464F-9811-19D6BE4C535C}</x14:id>
+          <x14:id>{B06110FD-9221-413D-A196-0D737E69324D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3936,7 +5342,20 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G3:G1048576</xm:sqref>
+          <xm:sqref>G54:G1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{B06110FD-9221-413D-A196-0D737E69324D}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G3:G53</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3949,7 +5368,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="B1:V1048572"/>
+  <dimension ref="B1:V1048571"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" customWidth="1"/>
@@ -4024,40 +5443,40 @@
         <v>5</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="P2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="R2" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S2" s="4" t="s">
         <v>8</v>
@@ -4075,7 +5494,7 @@
         <v>46023</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" s="7">
         <v>0</v>
@@ -4096,10 +5515,10 @@
         <v>0</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L3" s="7">
         <v>0</v>
@@ -4137,7 +5556,7 @@
         <v>46024</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="7">
         <v>0</v>
@@ -4158,10 +5577,10 @@
         <v>0</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L4" s="7">
         <v>0</v>
@@ -4199,7 +5618,7 @@
         <v>46025</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" s="11">
         <v>0</v>
@@ -4220,10 +5639,10 @@
         <v>0</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L5" s="11">
         <v>0</v>
@@ -4261,7 +5680,7 @@
         <v>46027</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" s="7">
         <v>0</v>
@@ -4282,10 +5701,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L6" s="7">
         <v>1</v>
@@ -4323,13 +5742,13 @@
         <v>46028</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" s="7">
         <v>13</v>
       </c>
       <c r="E7" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="7">
         <v>23</v>
@@ -4385,7 +5804,7 @@
         <v>46029</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" s="7">
         <v>0</v>
@@ -4406,10 +5825,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L8" s="7">
         <v>4</v>
@@ -4447,7 +5866,7 @@
         <v>46030</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
@@ -4468,10 +5887,10 @@
         <v>0</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L9" s="7">
         <v>7</v>
@@ -4509,13 +5928,13 @@
         <v>46031</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D10" s="7">
         <v>15</v>
       </c>
       <c r="E10" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="7">
         <v>35</v>
@@ -4571,7 +5990,7 @@
         <v>46032</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D11" s="11">
         <v>0</v>
@@ -4592,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L11" s="11">
         <v>0</v>
@@ -4633,7 +6052,7 @@
         <v>46034</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D12" s="7">
         <v>0</v>
@@ -4654,10 +6073,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L12" s="7">
         <v>0</v>
@@ -4695,7 +6114,7 @@
         <v>46035</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D13" s="7">
         <v>0</v>
@@ -4716,10 +6135,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L13" s="7">
         <v>1</v>
@@ -4728,7 +6147,7 @@
         <v>8</v>
       </c>
       <c r="N13" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13" s="7">
         <v>0</v>
@@ -4757,7 +6176,7 @@
         <v>46036</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" s="7">
         <v>0</v>
@@ -4778,10 +6197,10 @@
         <v>0</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L14" s="7">
         <v>2</v>
@@ -4819,13 +6238,13 @@
         <v>46037</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15" s="7">
         <v>47</v>
       </c>
       <c r="E15" s="7">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F15" s="7">
         <v>74</v>
@@ -4843,7 +6262,7 @@
         <v>4</v>
       </c>
       <c r="K15" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L15" s="7">
         <v>254</v>
@@ -4881,13 +6300,13 @@
         <v>46038</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" s="7">
         <v>31</v>
       </c>
       <c r="E16" s="7">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F16" s="7">
         <v>44</v>
@@ -4902,10 +6321,10 @@
         <v>2634832</v>
       </c>
       <c r="J16" s="7">
+        <v>6</v>
+      </c>
+      <c r="K16" s="7">
         <v>5</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>18</v>
       </c>
       <c r="L16" s="7">
         <v>169</v>
@@ -4943,7 +6362,7 @@
         <v>46039</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D17" s="11">
         <v>0</v>
@@ -4964,10 +6383,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L17" s="11">
         <v>0</v>
@@ -5005,7 +6424,7 @@
         <v>46041</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D18" s="7">
         <v>0</v>
@@ -5026,10 +6445,10 @@
         <v>0</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L18" s="7">
         <v>2</v>
@@ -5067,13 +6486,13 @@
         <v>46042</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D19" s="7">
         <v>17</v>
       </c>
       <c r="E19" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="7">
         <v>38</v>
@@ -5087,11 +6506,11 @@
       <c r="I19" s="8">
         <v>638900</v>
       </c>
-      <c r="J19" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>18</v>
+      <c r="J19" s="7">
+        <v>2</v>
+      </c>
+      <c r="K19" s="7">
+        <v>2</v>
       </c>
       <c r="L19" s="7">
         <v>104</v>
@@ -5129,7 +6548,7 @@
         <v>46043</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D20" s="7">
         <v>0</v>
@@ -5150,10 +6569,10 @@
         <v>0</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L20" s="7">
         <v>4</v>
@@ -5191,13 +6610,13 @@
         <v>46044</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D21" s="7">
         <v>27</v>
       </c>
       <c r="E21" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F21" s="7">
         <v>38</v>
@@ -5211,11 +6630,11 @@
       <c r="I21" s="8">
         <v>1019600</v>
       </c>
-      <c r="J21" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>18</v>
+      <c r="J21" s="7">
+        <v>5</v>
+      </c>
+      <c r="K21" s="7">
+        <v>5</v>
       </c>
       <c r="L21" s="7">
         <v>163</v>
@@ -5253,7 +6672,7 @@
         <v>46045</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D22" s="11">
         <v>28</v>
@@ -5273,11 +6692,11 @@
       <c r="I22" s="13">
         <v>1507000</v>
       </c>
-      <c r="J22" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>18</v>
+      <c r="J22" s="11">
+        <v>2</v>
+      </c>
+      <c r="K22" s="11">
+        <v>1</v>
       </c>
       <c r="L22" s="11">
         <v>187</v>
@@ -5315,7 +6734,7 @@
         <v>46046</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D23" s="11">
         <v>0</v>
@@ -5336,10 +6755,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L23" s="11">
         <v>0</v>
@@ -5377,7 +6796,7 @@
         <v>46048</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D24" s="7">
         <v>0</v>
@@ -5398,10 +6817,10 @@
         <v>0</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L24" s="7">
         <v>2</v>
@@ -5439,13 +6858,13 @@
         <v>46049</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D25" s="7">
         <v>8</v>
       </c>
       <c r="E25" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="7">
         <v>29</v>
@@ -5459,11 +6878,11 @@
       <c r="I25" s="8">
         <v>459700</v>
       </c>
-      <c r="J25" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>18</v>
+      <c r="J25" s="7">
+        <v>1</v>
+      </c>
+      <c r="K25" s="7">
+        <v>1</v>
       </c>
       <c r="L25" s="7">
         <v>72</v>
@@ -5501,13 +6920,13 @@
         <v>46050</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D26" s="7">
         <v>26</v>
       </c>
       <c r="E26" s="7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F26" s="7">
         <v>44</v>
@@ -5521,11 +6940,11 @@
       <c r="I26" s="8">
         <v>965000</v>
       </c>
-      <c r="J26" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>18</v>
+      <c r="J26" s="7">
+        <v>7</v>
+      </c>
+      <c r="K26" s="7">
+        <v>6</v>
       </c>
       <c r="L26" s="7">
         <v>189</v>
@@ -5563,13 +6982,13 @@
         <v>46051</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D27" s="7">
         <v>45</v>
       </c>
       <c r="E27" s="7">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F27" s="7">
         <v>69</v>
@@ -5583,11 +7002,11 @@
       <c r="I27" s="8">
         <v>1793700</v>
       </c>
-      <c r="J27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>18</v>
+      <c r="J27" s="7">
+        <v>10</v>
+      </c>
+      <c r="K27" s="7">
+        <v>9</v>
       </c>
       <c r="L27" s="7">
         <v>289</v>
@@ -5625,31 +7044,31 @@
         <v>46052</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D28" s="7">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E28" s="7">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F28" s="7">
         <v>54</v>
       </c>
       <c r="G28" s="9">
-        <v>0.72222222222222221</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H28" s="8">
         <v>3856435.9699999997</v>
       </c>
       <c r="I28" s="8">
-        <v>1981759</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>18</v>
+        <v>2277459</v>
+      </c>
+      <c r="J28" s="7">
+        <v>9</v>
+      </c>
+      <c r="K28" s="7">
+        <v>8</v>
       </c>
       <c r="L28" s="7">
         <v>147</v>
@@ -5687,31 +7106,31 @@
         <v>46053</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D29" s="11">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E29" s="11">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F29" s="11">
         <v>83</v>
       </c>
       <c r="G29" s="12">
-        <v>0.77108433734939763</v>
+        <v>0.67469879518072284</v>
       </c>
       <c r="H29" s="13">
         <v>4384104.28</v>
       </c>
       <c r="I29" s="13">
-        <v>3105300</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>18</v>
+        <v>2482100</v>
+      </c>
+      <c r="J29" s="11">
+        <v>7</v>
+      </c>
+      <c r="K29" s="11">
+        <v>7</v>
       </c>
       <c r="L29" s="11">
         <v>350</v>
@@ -5745,79 +7164,1520 @@
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B30" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="11">
-        <v>360</v>
-      </c>
-      <c r="E30" s="11">
-        <v>59</v>
-      </c>
-      <c r="F30" s="11">
-        <v>578</v>
-      </c>
-      <c r="G30" s="12">
-        <v>0.62283737024221453</v>
-      </c>
-      <c r="H30" s="13">
-        <v>38131180.57</v>
-      </c>
-      <c r="I30" s="13">
-        <v>19245991</v>
-      </c>
-      <c r="J30" s="11">
-        <v>13</v>
-      </c>
-      <c r="K30" s="11">
+      <c r="B30" s="6">
+        <v>46055</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="7">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="8">
+        <v>0</v>
+      </c>
+      <c r="I30" s="8">
+        <v>0</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L30" s="7">
+        <v>2</v>
+      </c>
+      <c r="M30" s="7">
+        <v>13</v>
+      </c>
+      <c r="N30" s="7">
+        <v>5</v>
+      </c>
+      <c r="O30" s="7">
+        <v>0</v>
+      </c>
+      <c r="P30" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="7">
+        <v>0</v>
+      </c>
+      <c r="R30" s="7">
+        <v>0</v>
+      </c>
+      <c r="S30" s="7">
+        <v>0</v>
+      </c>
+      <c r="T30" s="7">
+        <v>0</v>
+      </c>
+      <c r="U30" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B31" s="6">
+        <v>46056</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="7">
+        <v>0</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7">
+        <v>0</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="8">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8">
+        <v>0</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L31" s="7">
+        <v>2</v>
+      </c>
+      <c r="M31" s="7">
+        <v>10</v>
+      </c>
+      <c r="N31" s="7">
+        <v>9</v>
+      </c>
+      <c r="O31" s="7">
+        <v>0</v>
+      </c>
+      <c r="P31" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="7">
+        <v>0</v>
+      </c>
+      <c r="R31" s="7">
+        <v>0</v>
+      </c>
+      <c r="S31" s="7">
+        <v>0</v>
+      </c>
+      <c r="T31" s="7">
+        <v>0</v>
+      </c>
+      <c r="U31" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B32" s="6">
+        <v>46057</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="7">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="8">
+        <v>0</v>
+      </c>
+      <c r="I32" s="8">
+        <v>0</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L32" s="7">
+        <v>0</v>
+      </c>
+      <c r="M32" s="7">
+        <v>14</v>
+      </c>
+      <c r="N32" s="7">
+        <v>10</v>
+      </c>
+      <c r="O32" s="7">
+        <v>0</v>
+      </c>
+      <c r="P32" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="7">
+        <v>0</v>
+      </c>
+      <c r="R32" s="7">
+        <v>0</v>
+      </c>
+      <c r="S32" s="7">
+        <v>0</v>
+      </c>
+      <c r="T32" s="7">
+        <v>0</v>
+      </c>
+      <c r="U32" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B33" s="6">
+        <v>46058</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="7">
+        <v>14</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0</v>
+      </c>
+      <c r="F33" s="7">
+        <v>25</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H33" s="8">
+        <v>1330120.6300000001</v>
+      </c>
+      <c r="I33" s="8">
+        <v>626100</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L33" s="7">
+        <v>76</v>
+      </c>
+      <c r="M33" s="7">
+        <v>5</v>
+      </c>
+      <c r="N33" s="7">
+        <v>2</v>
+      </c>
+      <c r="O33" s="7">
+        <v>0</v>
+      </c>
+      <c r="P33" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="7">
+        <v>0</v>
+      </c>
+      <c r="R33" s="7">
+        <v>0</v>
+      </c>
+      <c r="S33" s="7">
+        <v>0</v>
+      </c>
+      <c r="T33" s="7">
+        <v>0</v>
+      </c>
+      <c r="U33" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B34" s="6">
+        <v>46059</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="7">
+        <v>2</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7">
+        <v>3</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H34" s="8">
+        <v>892252.98</v>
+      </c>
+      <c r="I34" s="8">
+        <v>499625</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L34" s="7">
+        <v>15</v>
+      </c>
+      <c r="M34" s="7">
+        <v>9</v>
+      </c>
+      <c r="N34" s="7">
         <v>4</v>
       </c>
-      <c r="L30" s="11">
-        <v>2197</v>
-      </c>
-      <c r="M30" s="11">
-        <v>211</v>
-      </c>
-      <c r="N30" s="11">
-        <v>98</v>
-      </c>
-      <c r="O30" s="11">
-        <v>0</v>
-      </c>
-      <c r="P30" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="11">
-        <v>0</v>
-      </c>
-      <c r="R30" s="11">
-        <v>0</v>
-      </c>
-      <c r="S30" s="11">
-        <v>0</v>
-      </c>
-      <c r="T30" s="11">
-        <v>0</v>
-      </c>
-      <c r="U30" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1048572" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G1048572" s="3">
+      <c r="O34" s="7">
+        <v>0</v>
+      </c>
+      <c r="P34" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="7">
+        <v>0</v>
+      </c>
+      <c r="R34" s="7">
+        <v>0</v>
+      </c>
+      <c r="S34" s="7">
+        <v>0</v>
+      </c>
+      <c r="T34" s="7">
+        <v>0</v>
+      </c>
+      <c r="U34" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B35" s="10">
+        <v>46060</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="11">
+        <v>0</v>
+      </c>
+      <c r="E35" s="11">
+        <v>0</v>
+      </c>
+      <c r="F35" s="11">
+        <v>0</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="13">
+        <v>0</v>
+      </c>
+      <c r="I35" s="13">
+        <v>0</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L35" s="11">
+        <v>0</v>
+      </c>
+      <c r="M35" s="11">
+        <v>6</v>
+      </c>
+      <c r="N35" s="11">
+        <v>1</v>
+      </c>
+      <c r="O35" s="11">
+        <v>0</v>
+      </c>
+      <c r="P35" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="11">
+        <v>0</v>
+      </c>
+      <c r="R35" s="11">
+        <v>0</v>
+      </c>
+      <c r="S35" s="11">
+        <v>0</v>
+      </c>
+      <c r="T35" s="11">
+        <v>0</v>
+      </c>
+      <c r="U35" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B36" s="6">
+        <v>46062</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="7">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7">
+        <v>0</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="8">
+        <v>0</v>
+      </c>
+      <c r="I36" s="8">
+        <v>0</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L36" s="7">
+        <v>0</v>
+      </c>
+      <c r="M36" s="7">
+        <v>10</v>
+      </c>
+      <c r="N36" s="7">
+        <v>3</v>
+      </c>
+      <c r="O36" s="7">
+        <v>0</v>
+      </c>
+      <c r="P36" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="7">
+        <v>0</v>
+      </c>
+      <c r="R36" s="7">
+        <v>0</v>
+      </c>
+      <c r="S36" s="7">
+        <v>0</v>
+      </c>
+      <c r="T36" s="7">
+        <v>0</v>
+      </c>
+      <c r="U36" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B37" s="6">
+        <v>46063</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" s="7">
+        <v>36</v>
+      </c>
+      <c r="E37" s="7">
+        <v>7</v>
+      </c>
+      <c r="F37" s="7">
+        <v>70</v>
+      </c>
+      <c r="G37" s="9">
+        <v>0.51428571428571423</v>
+      </c>
+      <c r="H37" s="8">
+        <v>3031093.4099999992</v>
+      </c>
+      <c r="I37" s="8">
+        <v>1647054.5</v>
+      </c>
+      <c r="J37" s="7">
+        <v>5</v>
+      </c>
+      <c r="K37" s="7">
+        <v>5</v>
+      </c>
+      <c r="L37" s="7">
+        <v>285</v>
+      </c>
+      <c r="M37" s="7">
+        <v>7</v>
+      </c>
+      <c r="N37" s="7">
+        <v>0</v>
+      </c>
+      <c r="O37" s="7">
+        <v>0</v>
+      </c>
+      <c r="P37" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="7">
+        <v>0</v>
+      </c>
+      <c r="R37" s="7">
+        <v>0</v>
+      </c>
+      <c r="S37" s="7">
+        <v>0</v>
+      </c>
+      <c r="T37" s="7">
+        <v>0</v>
+      </c>
+      <c r="U37" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B38" s="6">
+        <v>46064</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="7">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="8">
+        <v>0</v>
+      </c>
+      <c r="I38" s="8">
+        <v>0</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L38" s="7">
+        <v>3</v>
+      </c>
+      <c r="M38" s="7">
+        <v>13</v>
+      </c>
+      <c r="N38" s="7">
+        <v>1</v>
+      </c>
+      <c r="O38" s="7">
+        <v>0</v>
+      </c>
+      <c r="P38" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="7">
+        <v>0</v>
+      </c>
+      <c r="R38" s="7">
+        <v>0</v>
+      </c>
+      <c r="S38" s="7">
+        <v>0</v>
+      </c>
+      <c r="T38" s="7">
+        <v>0</v>
+      </c>
+      <c r="U38" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B39" s="6">
+        <v>46065</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="7">
+        <v>0</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7">
+        <v>58</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0</v>
+      </c>
+      <c r="H39" s="8">
+        <v>2957672</v>
+      </c>
+      <c r="I39" s="8">
+        <v>0</v>
+      </c>
+      <c r="J39" s="7">
+        <v>3</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L39" s="7">
+        <v>112</v>
+      </c>
+      <c r="M39" s="7">
+        <v>8</v>
+      </c>
+      <c r="N39" s="7">
+        <v>0</v>
+      </c>
+      <c r="O39" s="7">
+        <v>0</v>
+      </c>
+      <c r="P39" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="7">
+        <v>0</v>
+      </c>
+      <c r="R39" s="7">
+        <v>0</v>
+      </c>
+      <c r="S39" s="7">
+        <v>0</v>
+      </c>
+      <c r="T39" s="7">
+        <v>0</v>
+      </c>
+      <c r="U39" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B40" s="6">
+        <v>46066</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7">
+        <v>26</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="8">
+        <v>3193549</v>
+      </c>
+      <c r="I40" s="8">
+        <v>0</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L40" s="7">
+        <v>6</v>
+      </c>
+      <c r="M40" s="7">
+        <v>0</v>
+      </c>
+      <c r="N40" s="7">
+        <v>0</v>
+      </c>
+      <c r="O40" s="7">
+        <v>0</v>
+      </c>
+      <c r="P40" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="7">
+        <v>0</v>
+      </c>
+      <c r="R40" s="7">
+        <v>0</v>
+      </c>
+      <c r="S40" s="7">
+        <v>0</v>
+      </c>
+      <c r="T40" s="7">
+        <v>0</v>
+      </c>
+      <c r="U40" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B41" s="10">
+        <v>46067</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="11">
+        <v>0</v>
+      </c>
+      <c r="E41" s="11">
+        <v>0</v>
+      </c>
+      <c r="F41" s="11">
+        <v>0</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="13">
+        <v>0</v>
+      </c>
+      <c r="I41" s="13">
+        <v>0</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L41" s="11">
+        <v>0</v>
+      </c>
+      <c r="M41" s="11">
+        <v>0</v>
+      </c>
+      <c r="N41" s="11">
+        <v>0</v>
+      </c>
+      <c r="O41" s="11">
+        <v>0</v>
+      </c>
+      <c r="P41" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="11">
+        <v>0</v>
+      </c>
+      <c r="R41" s="11">
+        <v>0</v>
+      </c>
+      <c r="S41" s="11">
+        <v>0</v>
+      </c>
+      <c r="T41" s="11">
+        <v>0</v>
+      </c>
+      <c r="U41" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B42" s="6">
+        <v>46069</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="7">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7">
+        <v>0</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="8">
+        <v>0</v>
+      </c>
+      <c r="I42" s="8">
+        <v>0</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L42" s="7">
+        <v>0</v>
+      </c>
+      <c r="M42" s="7">
+        <v>0</v>
+      </c>
+      <c r="N42" s="7">
+        <v>0</v>
+      </c>
+      <c r="O42" s="7">
+        <v>0</v>
+      </c>
+      <c r="P42" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="7">
+        <v>0</v>
+      </c>
+      <c r="R42" s="7">
+        <v>0</v>
+      </c>
+      <c r="S42" s="7">
+        <v>0</v>
+      </c>
+      <c r="T42" s="7">
+        <v>0</v>
+      </c>
+      <c r="U42" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B43" s="6">
+        <v>46070</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" s="7">
+        <v>0</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0</v>
+      </c>
+      <c r="F43" s="7">
+        <v>0</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="8">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8">
+        <v>0</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43" s="7">
+        <v>0</v>
+      </c>
+      <c r="M43" s="7">
+        <v>0</v>
+      </c>
+      <c r="N43" s="7">
+        <v>0</v>
+      </c>
+      <c r="O43" s="7">
+        <v>0</v>
+      </c>
+      <c r="P43" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="7">
+        <v>0</v>
+      </c>
+      <c r="R43" s="7">
+        <v>0</v>
+      </c>
+      <c r="S43" s="7">
+        <v>0</v>
+      </c>
+      <c r="T43" s="7">
+        <v>0</v>
+      </c>
+      <c r="U43" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B44" s="6">
+        <v>46071</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="7">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7">
+        <v>0</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="8">
+        <v>0</v>
+      </c>
+      <c r="I44" s="8">
+        <v>0</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L44" s="7">
+        <v>0</v>
+      </c>
+      <c r="M44" s="7">
+        <v>0</v>
+      </c>
+      <c r="N44" s="7">
+        <v>0</v>
+      </c>
+      <c r="O44" s="7">
+        <v>0</v>
+      </c>
+      <c r="P44" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="7">
+        <v>0</v>
+      </c>
+      <c r="R44" s="7">
+        <v>0</v>
+      </c>
+      <c r="S44" s="7">
+        <v>0</v>
+      </c>
+      <c r="T44" s="7">
+        <v>0</v>
+      </c>
+      <c r="U44" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B45" s="6">
+        <v>46072</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="7">
+        <v>0</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0</v>
+      </c>
+      <c r="F45" s="7">
+        <v>54</v>
+      </c>
+      <c r="G45" s="9">
+        <v>0</v>
+      </c>
+      <c r="H45" s="8">
+        <v>2889841</v>
+      </c>
+      <c r="I45" s="8">
+        <v>0</v>
+      </c>
+      <c r="J45" s="7">
+        <v>1</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L45" s="7">
+        <v>22</v>
+      </c>
+      <c r="M45" s="7">
+        <v>0</v>
+      </c>
+      <c r="N45" s="7">
+        <v>0</v>
+      </c>
+      <c r="O45" s="7">
+        <v>0</v>
+      </c>
+      <c r="P45" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="7">
+        <v>0</v>
+      </c>
+      <c r="R45" s="7">
+        <v>0</v>
+      </c>
+      <c r="S45" s="7">
+        <v>0</v>
+      </c>
+      <c r="T45" s="7">
+        <v>0</v>
+      </c>
+      <c r="U45" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B46" s="6">
+        <v>46073</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" s="8">
+        <v>0</v>
+      </c>
+      <c r="I46" s="8">
+        <v>0</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L46" s="7">
+        <v>0</v>
+      </c>
+      <c r="M46" s="7">
+        <v>0</v>
+      </c>
+      <c r="N46" s="7">
+        <v>0</v>
+      </c>
+      <c r="O46" s="7">
+        <v>0</v>
+      </c>
+      <c r="P46" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="7">
+        <v>0</v>
+      </c>
+      <c r="R46" s="7">
+        <v>0</v>
+      </c>
+      <c r="S46" s="7">
+        <v>0</v>
+      </c>
+      <c r="T46" s="7">
+        <v>0</v>
+      </c>
+      <c r="U46" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B47" s="10">
+        <v>46074</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="11">
+        <v>0</v>
+      </c>
+      <c r="E47" s="11">
+        <v>0</v>
+      </c>
+      <c r="F47" s="11">
+        <v>0</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" s="13">
+        <v>0</v>
+      </c>
+      <c r="I47" s="13">
+        <v>0</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47" s="11">
+        <v>0</v>
+      </c>
+      <c r="M47" s="11">
+        <v>0</v>
+      </c>
+      <c r="N47" s="11">
+        <v>0</v>
+      </c>
+      <c r="O47" s="11">
+        <v>0</v>
+      </c>
+      <c r="P47" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="11">
+        <v>0</v>
+      </c>
+      <c r="R47" s="11">
+        <v>0</v>
+      </c>
+      <c r="S47" s="11">
+        <v>0</v>
+      </c>
+      <c r="T47" s="11">
+        <v>0</v>
+      </c>
+      <c r="U47" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B48" s="6">
+        <v>46076</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="7">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="8">
+        <v>0</v>
+      </c>
+      <c r="I48" s="8">
+        <v>0</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L48" s="7">
+        <v>0</v>
+      </c>
+      <c r="M48" s="7">
+        <v>0</v>
+      </c>
+      <c r="N48" s="7">
+        <v>0</v>
+      </c>
+      <c r="O48" s="7">
+        <v>0</v>
+      </c>
+      <c r="P48" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="7">
+        <v>0</v>
+      </c>
+      <c r="R48" s="7">
+        <v>0</v>
+      </c>
+      <c r="S48" s="7">
+        <v>0</v>
+      </c>
+      <c r="T48" s="7">
+        <v>0</v>
+      </c>
+      <c r="U48" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B49" s="6">
+        <v>46077</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" s="7">
+        <v>0</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0</v>
+      </c>
+      <c r="F49" s="7">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" s="8">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8">
+        <v>0</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49" s="7">
+        <v>0</v>
+      </c>
+      <c r="M49" s="7">
+        <v>0</v>
+      </c>
+      <c r="N49" s="7">
+        <v>0</v>
+      </c>
+      <c r="O49" s="7">
+        <v>0</v>
+      </c>
+      <c r="P49" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="7">
+        <v>0</v>
+      </c>
+      <c r="R49" s="7">
+        <v>0</v>
+      </c>
+      <c r="S49" s="7">
+        <v>0</v>
+      </c>
+      <c r="T49" s="7">
+        <v>0</v>
+      </c>
+      <c r="U49" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B50" s="6">
+        <v>46078</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" s="7">
+        <v>0</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="8">
+        <v>0</v>
+      </c>
+      <c r="I50" s="8">
+        <v>0</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L50" s="7">
+        <v>0</v>
+      </c>
+      <c r="M50" s="7">
+        <v>0</v>
+      </c>
+      <c r="N50" s="7">
+        <v>0</v>
+      </c>
+      <c r="O50" s="7">
+        <v>0</v>
+      </c>
+      <c r="P50" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="7">
+        <v>0</v>
+      </c>
+      <c r="R50" s="7">
+        <v>0</v>
+      </c>
+      <c r="S50" s="7">
+        <v>0</v>
+      </c>
+      <c r="T50" s="7">
+        <v>0</v>
+      </c>
+      <c r="U50" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B51" s="6">
+        <v>46079</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" s="7">
+        <v>0</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0</v>
+      </c>
+      <c r="F51" s="7">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" s="8">
+        <v>0</v>
+      </c>
+      <c r="I51" s="8">
+        <v>0</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L51" s="7">
+        <v>0</v>
+      </c>
+      <c r="M51" s="7">
+        <v>0</v>
+      </c>
+      <c r="N51" s="7">
+        <v>0</v>
+      </c>
+      <c r="O51" s="7">
+        <v>0</v>
+      </c>
+      <c r="P51" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="7">
+        <v>0</v>
+      </c>
+      <c r="R51" s="7">
+        <v>0</v>
+      </c>
+      <c r="S51" s="7">
+        <v>0</v>
+      </c>
+      <c r="T51" s="7">
+        <v>0</v>
+      </c>
+      <c r="U51" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B52" s="6">
+        <v>46080</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" s="7">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" s="8">
+        <v>0</v>
+      </c>
+      <c r="I52" s="8">
+        <v>0</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L52" s="7">
+        <v>0</v>
+      </c>
+      <c r="M52" s="7">
+        <v>0</v>
+      </c>
+      <c r="N52" s="7">
+        <v>0</v>
+      </c>
+      <c r="O52" s="7">
+        <v>0</v>
+      </c>
+      <c r="P52" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="7">
+        <v>0</v>
+      </c>
+      <c r="R52" s="7">
+        <v>0</v>
+      </c>
+      <c r="S52" s="7">
+        <v>0</v>
+      </c>
+      <c r="T52" s="7">
+        <v>0</v>
+      </c>
+      <c r="U52" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B53" s="10">
+        <v>46081</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" s="11">
+        <v>0</v>
+      </c>
+      <c r="E53" s="11">
+        <v>0</v>
+      </c>
+      <c r="F53" s="11">
+        <v>0</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" s="13">
+        <v>0</v>
+      </c>
+      <c r="I53" s="13">
+        <v>0</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L53" s="11">
+        <v>0</v>
+      </c>
+      <c r="M53" s="11">
+        <v>0</v>
+      </c>
+      <c r="N53" s="11">
+        <v>0</v>
+      </c>
+      <c r="O53" s="11">
+        <v>0</v>
+      </c>
+      <c r="P53" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="11">
+        <v>0</v>
+      </c>
+      <c r="R53" s="11">
+        <v>0</v>
+      </c>
+      <c r="S53" s="11">
+        <v>0</v>
+      </c>
+      <c r="T53" s="11">
+        <v>0</v>
+      </c>
+      <c r="U53" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1048571" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G1048571" s="3">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="R1:U1"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
-  <conditionalFormatting sqref="G3:G1048576">
+  <conditionalFormatting sqref="G54:G1048576">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5CF184F6-6AE3-43F4-801C-B56A52ADB053}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G53">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -5826,7 +8686,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5CF184F6-6AE3-43F4-801C-B56A52ADB053}</x14:id>
+          <x14:id>{47528C65-6657-42A6-B1FC-D978789A73DE}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5851,7 +8711,20 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G3:G1048576</xm:sqref>
+          <xm:sqref>G54:G1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{47528C65-6657-42A6-B1FC-D978789A73DE}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G3:G53</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5864,7 +8737,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="B1:V1048576"/>
+  <dimension ref="B1:V1048575"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" customWidth="1"/>
@@ -5938,40 +8811,40 @@
         <v>5</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="P2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="R2" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S2" s="4" t="s">
         <v>8</v>
@@ -5983,7 +8856,7 @@
         <v>10</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="2:22" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -5991,7 +8864,7 @@
         <v>46023</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" s="7">
         <v>0</v>
@@ -6012,10 +8885,10 @@
         <v>0</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L3" s="7">
         <v>0</v>
@@ -6056,13 +8929,13 @@
         <v>46024</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="7">
         <v>70</v>
       </c>
       <c r="E4" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" s="7">
         <v>138</v>
@@ -6121,7 +8994,7 @@
         <v>46025</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" s="11">
         <v>0</v>
@@ -6142,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L5" s="11">
         <v>0</v>
@@ -6186,13 +9059,13 @@
         <v>46027</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" s="7">
         <v>8</v>
       </c>
       <c r="E6" s="7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6" s="7">
         <v>15</v>
@@ -6216,10 +9089,10 @@
         <v>82</v>
       </c>
       <c r="M6" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N6" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O6" s="7">
         <v>0</v>
@@ -6251,13 +9124,13 @@
         <v>46028</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" s="7">
         <v>70</v>
       </c>
       <c r="E7" s="7">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F7" s="7">
         <v>117</v>
@@ -6281,10 +9154,10 @@
         <v>907</v>
       </c>
       <c r="M7" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N7" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O7" s="7">
         <v>0</v>
@@ -6316,13 +9189,13 @@
         <v>46029</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" s="7">
         <v>42</v>
       </c>
       <c r="E8" s="7">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F8" s="7">
         <v>79</v>
@@ -6337,7 +9210,7 @@
         <v>1522700</v>
       </c>
       <c r="J8" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K8" s="7">
         <v>8</v>
@@ -6381,13 +9254,13 @@
         <v>46030</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D9" s="7">
         <v>84</v>
       </c>
       <c r="E9" s="7">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="F9" s="7">
         <v>123</v>
@@ -6411,10 +9284,10 @@
         <v>783</v>
       </c>
       <c r="M9" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N9" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O9" s="7">
         <v>0</v>
@@ -6446,40 +9319,40 @@
         <v>46031</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D10" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E10" s="7">
-        <v>5</v>
+        <v>130</v>
       </c>
       <c r="F10" s="7">
         <v>459</v>
       </c>
       <c r="G10" s="9">
-        <v>0.73856209150326801</v>
+        <v>0.73638344226579522</v>
       </c>
       <c r="H10" s="8">
         <v>7110364.3600000013</v>
       </c>
       <c r="I10" s="8">
-        <v>4561180</v>
+        <v>4555680</v>
       </c>
       <c r="J10" s="7">
         <v>50</v>
       </c>
       <c r="K10" s="7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L10" s="7">
         <v>2114</v>
       </c>
       <c r="M10" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N10" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O10" s="7">
         <v>0</v>
@@ -6511,7 +9384,7 @@
         <v>46032</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D11" s="11">
         <v>0</v>
@@ -6532,10 +9405,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L11" s="11">
         <v>0</v>
@@ -6544,7 +9417,7 @@
         <v>121</v>
       </c>
       <c r="N11" s="11">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O11" s="11">
         <v>0</v>
@@ -6576,13 +9449,13 @@
         <v>46034</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D12" s="7">
         <v>68</v>
       </c>
       <c r="E12" s="7">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="F12" s="7">
         <v>117</v>
@@ -6600,16 +9473,16 @@
         <v>33</v>
       </c>
       <c r="K12" s="7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L12" s="7">
         <v>748</v>
       </c>
       <c r="M12" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N12" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O12" s="7">
         <v>0</v>
@@ -6641,13 +9514,13 @@
         <v>46035</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D13" s="7">
         <v>97</v>
       </c>
       <c r="E13" s="7">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="F13" s="7">
         <v>172</v>
@@ -6665,7 +9538,7 @@
         <v>78</v>
       </c>
       <c r="K13" s="7">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="L13" s="7">
         <v>1271</v>
@@ -6706,13 +9579,13 @@
         <v>46036</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" s="7">
         <v>61</v>
       </c>
       <c r="E14" s="7">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F14" s="7">
         <v>100</v>
@@ -6730,13 +9603,13 @@
         <v>43</v>
       </c>
       <c r="K14" s="7">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L14" s="7">
         <v>778</v>
       </c>
       <c r="M14" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N14" s="7">
         <v>353</v>
@@ -6771,13 +9644,13 @@
         <v>46037</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15" s="7">
         <v>127</v>
       </c>
       <c r="E15" s="7">
-        <v>9</v>
+        <v>218</v>
       </c>
       <c r="F15" s="7">
         <v>182</v>
@@ -6795,7 +9668,7 @@
         <v>140</v>
       </c>
       <c r="K15" s="7">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="L15" s="7">
         <v>1836</v>
@@ -6836,37 +9709,37 @@
         <v>46038</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" s="7">
         <v>139</v>
       </c>
       <c r="E16" s="7">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="F16" s="7">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G16" s="9">
-        <v>0.51672862453531598</v>
+        <v>0.52452830188679245</v>
       </c>
       <c r="H16" s="8">
-        <v>10235078.33</v>
+        <v>9964678.3299999982</v>
       </c>
       <c r="I16" s="8">
         <v>5167750</v>
       </c>
       <c r="J16" s="7">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="K16" s="7">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="L16" s="7">
         <v>1710</v>
       </c>
       <c r="M16" s="7">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N16" s="7">
         <v>202</v>
@@ -6901,7 +9774,7 @@
         <v>46039</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D17" s="11">
         <v>0</v>
@@ -6910,31 +9783,31 @@
         <v>0</v>
       </c>
       <c r="F17" s="11">
-        <v>43</v>
-      </c>
-      <c r="G17" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="H17" s="13">
-        <v>304500</v>
+        <v>0</v>
       </c>
       <c r="I17" s="13">
         <v>0</v>
       </c>
-      <c r="J17" s="11">
-        <v>9</v>
+      <c r="J17" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L17" s="11">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="M17" s="11">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N17" s="11">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O17" s="11">
         <v>0</v>
@@ -6952,7 +9825,7 @@
         <v>312444</v>
       </c>
       <c r="T17" s="20">
-        <v>6.23</v>
+        <v>6.2300000000000013</v>
       </c>
       <c r="U17" s="12">
         <v>2.371304937844862E-2</v>
@@ -6966,13 +9839,13 @@
         <v>46041</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D18" s="7">
         <v>103</v>
       </c>
       <c r="E18" s="7">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="F18" s="7">
         <v>148</v>
@@ -6987,19 +9860,19 @@
         <v>2850300</v>
       </c>
       <c r="J18" s="7">
-        <v>16</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>18</v>
+        <v>103</v>
+      </c>
+      <c r="K18" s="7">
+        <v>92</v>
       </c>
       <c r="L18" s="7">
         <v>945</v>
       </c>
       <c r="M18" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N18" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O18" s="7">
         <v>0</v>
@@ -7031,13 +9904,13 @@
         <v>46042</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D19" s="7">
         <v>108</v>
       </c>
       <c r="E19" s="7">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="F19" s="7">
         <v>157</v>
@@ -7052,10 +9925,10 @@
         <v>1128790</v>
       </c>
       <c r="J19" s="7">
-        <v>22</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>18</v>
+        <v>79</v>
+      </c>
+      <c r="K19" s="7">
+        <v>65</v>
       </c>
       <c r="L19" s="7">
         <v>866</v>
@@ -7064,7 +9937,7 @@
         <v>237</v>
       </c>
       <c r="N19" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O19" s="7">
         <v>0</v>
@@ -7096,13 +9969,13 @@
         <v>46043</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D20" s="7">
         <v>107</v>
       </c>
       <c r="E20" s="7">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="F20" s="7">
         <v>155</v>
@@ -7117,19 +9990,19 @@
         <v>3011600</v>
       </c>
       <c r="J20" s="7">
-        <v>9</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>18</v>
+        <v>69</v>
+      </c>
+      <c r="K20" s="7">
+        <v>65</v>
       </c>
       <c r="L20" s="7">
         <v>1125</v>
       </c>
       <c r="M20" s="7">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="N20" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="O20" s="7">
         <v>0</v>
@@ -7147,7 +10020,7 @@
         <v>362290</v>
       </c>
       <c r="T20" s="19">
-        <v>12.010000000000002</v>
+        <v>12.01</v>
       </c>
       <c r="U20" s="9">
         <v>2.7157801761020176E-2</v>
@@ -7161,13 +10034,13 @@
         <v>46044</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D21" s="7">
         <v>297</v>
       </c>
       <c r="E21" s="7">
-        <v>7</v>
+        <v>266</v>
       </c>
       <c r="F21" s="7">
         <v>415</v>
@@ -7182,19 +10055,19 @@
         <v>2105700</v>
       </c>
       <c r="J21" s="7">
-        <v>20</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>18</v>
+        <v>108</v>
+      </c>
+      <c r="K21" s="7">
+        <v>78</v>
       </c>
       <c r="L21" s="7">
         <v>1887</v>
       </c>
       <c r="M21" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N21" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O21" s="7">
         <v>0</v>
@@ -7226,37 +10099,37 @@
         <v>46045</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D22" s="11">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E22" s="11">
-        <v>23</v>
+        <v>232</v>
       </c>
       <c r="F22" s="11">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="G22" s="12">
-        <v>0.67373572593800979</v>
+        <v>0.67487684729064035</v>
       </c>
       <c r="H22" s="13">
-        <v>9269835.5099999979</v>
+        <v>8999435.5099999979</v>
       </c>
       <c r="I22" s="13">
-        <v>4893350</v>
+        <v>4887250</v>
       </c>
       <c r="J22" s="11">
-        <v>7</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>18</v>
+        <v>131</v>
+      </c>
+      <c r="K22" s="11">
+        <v>93</v>
       </c>
       <c r="L22" s="11">
         <v>2908</v>
       </c>
       <c r="M22" s="11">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N22" s="11">
         <v>223</v>
@@ -7291,13 +10164,13 @@
         <v>46046</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D23" s="11">
         <v>59</v>
       </c>
       <c r="E23" s="11">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="F23" s="11">
         <v>115</v>
@@ -7311,11 +10184,11 @@
       <c r="I23" s="13">
         <v>1919400</v>
       </c>
-      <c r="J23" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>18</v>
+      <c r="J23" s="11">
+        <v>87</v>
+      </c>
+      <c r="K23" s="11">
+        <v>64</v>
       </c>
       <c r="L23" s="11">
         <v>882</v>
@@ -7324,7 +10197,7 @@
         <v>206</v>
       </c>
       <c r="N23" s="11">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O23" s="11">
         <v>0</v>
@@ -7356,40 +10229,40 @@
         <v>46048</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D24" s="7">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E24" s="7">
-        <v>251</v>
+        <v>357</v>
       </c>
       <c r="F24" s="7">
         <v>337</v>
       </c>
       <c r="G24" s="9">
-        <v>0.70029673590504449</v>
+        <v>0.6943620178041543</v>
       </c>
       <c r="H24" s="8">
         <v>4560880.8599999994</v>
       </c>
       <c r="I24" s="8">
-        <v>1784100</v>
+        <v>1771600</v>
       </c>
       <c r="J24" s="7">
-        <v>10</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>18</v>
+        <v>134</v>
+      </c>
+      <c r="K24" s="7">
+        <v>120</v>
       </c>
       <c r="L24" s="7">
         <v>1586</v>
       </c>
       <c r="M24" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="N24" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="O24" s="7">
         <v>0</v>
@@ -7421,13 +10294,13 @@
         <v>46049</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D25" s="7">
         <v>249</v>
       </c>
       <c r="E25" s="7">
-        <v>191</v>
+        <v>306</v>
       </c>
       <c r="F25" s="7">
         <v>342</v>
@@ -7442,19 +10315,19 @@
         <v>2640600</v>
       </c>
       <c r="J25" s="7">
-        <v>5</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>18</v>
+        <v>134</v>
+      </c>
+      <c r="K25" s="7">
+        <v>107</v>
       </c>
       <c r="L25" s="7">
         <v>1990</v>
       </c>
       <c r="M25" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="N25" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="O25" s="7">
         <v>0</v>
@@ -7472,7 +10345,7 @@
         <v>572817</v>
       </c>
       <c r="T25" s="19">
-        <v>15.690000000000001</v>
+        <v>15.690000000000003</v>
       </c>
       <c r="U25" s="9">
         <v>2.3019568204155953E-2</v>
@@ -7486,31 +10359,31 @@
         <v>46050</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D26" s="7">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="E26" s="7">
-        <v>285</v>
+        <v>739</v>
       </c>
       <c r="F26" s="7">
         <v>1220</v>
       </c>
       <c r="G26" s="9">
-        <v>0.79508196721311475</v>
+        <v>0.79016393442622945</v>
       </c>
       <c r="H26" s="8">
         <v>9306518.3900000006</v>
       </c>
       <c r="I26" s="8">
-        <v>5156165</v>
+        <v>5222793</v>
       </c>
       <c r="J26" s="7">
-        <v>85</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>18</v>
+        <v>376</v>
+      </c>
+      <c r="K26" s="7">
+        <v>325</v>
       </c>
       <c r="L26" s="7">
         <v>4133</v>
@@ -7519,7 +10392,7 @@
         <v>258</v>
       </c>
       <c r="N26" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O26" s="7">
         <v>0</v>
@@ -7537,7 +10410,7 @@
         <v>476250</v>
       </c>
       <c r="T26" s="19">
-        <v>14.170000000000007</v>
+        <v>14.170000000000005</v>
       </c>
       <c r="U26" s="9">
         <v>2.3090813648293962E-2</v>
@@ -7551,40 +10424,40 @@
         <v>46051</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D27" s="7">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E27" s="7">
-        <v>64</v>
+        <v>213</v>
       </c>
       <c r="F27" s="7">
         <v>335</v>
       </c>
       <c r="G27" s="9">
-        <v>0.67462686567164176</v>
+        <v>0.67164179104477617</v>
       </c>
       <c r="H27" s="8">
         <v>4078815.7899999991</v>
       </c>
       <c r="I27" s="8">
-        <v>2711558</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>18</v>
+        <v>2678558</v>
+      </c>
+      <c r="J27" s="7">
+        <v>170</v>
+      </c>
+      <c r="K27" s="7">
+        <v>141</v>
       </c>
       <c r="L27" s="7">
         <v>1794</v>
       </c>
       <c r="M27" s="7">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="N27" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O27" s="7">
         <v>0</v>
@@ -7616,40 +10489,40 @@
         <v>46052</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D28" s="7">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E28" s="7">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="F28" s="7">
         <v>173</v>
       </c>
       <c r="G28" s="9">
-        <v>0.61849710982658956</v>
+        <v>0.54335260115606931</v>
       </c>
       <c r="H28" s="8">
         <v>8257668.629999998</v>
       </c>
       <c r="I28" s="8">
-        <v>3742415</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>18</v>
+        <v>3788915</v>
+      </c>
+      <c r="J28" s="7">
+        <v>94</v>
+      </c>
+      <c r="K28" s="7">
+        <v>70</v>
       </c>
       <c r="L28" s="7">
         <v>1258</v>
       </c>
       <c r="M28" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N28" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O28" s="7">
         <v>0</v>
@@ -7681,40 +10554,40 @@
         <v>46053</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D29" s="11">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="E29" s="11">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="F29" s="11">
         <v>403</v>
       </c>
       <c r="G29" s="12">
-        <v>0.66004962779156329</v>
+        <v>0.64019851116625315</v>
       </c>
       <c r="H29" s="13">
         <v>10481569.890000001</v>
       </c>
       <c r="I29" s="13">
-        <v>6110354.1200000001</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>18</v>
+        <v>5909354.1200000001</v>
+      </c>
+      <c r="J29" s="11">
+        <v>112</v>
+      </c>
+      <c r="K29" s="11">
+        <v>97</v>
       </c>
       <c r="L29" s="11">
         <v>2357</v>
       </c>
       <c r="M29" s="11">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N29" s="11">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="O29" s="11">
         <v>0</v>
@@ -7742,86 +10615,1579 @@
       </c>
     </row>
     <row r="30" spans="2:22" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="11">
-        <v>4246</v>
-      </c>
-      <c r="E30" s="11">
-        <v>999</v>
-      </c>
-      <c r="F30" s="11">
-        <v>6227</v>
-      </c>
-      <c r="G30" s="12">
-        <v>0.68186927894652316</v>
-      </c>
-      <c r="H30" s="13">
-        <v>126065343.33000003</v>
-      </c>
-      <c r="I30" s="13">
-        <v>66101962.119999997</v>
-      </c>
-      <c r="J30" s="11">
-        <v>677</v>
-      </c>
-      <c r="K30" s="11">
-        <v>354</v>
-      </c>
-      <c r="L30" s="11">
-        <v>33040</v>
-      </c>
-      <c r="M30" s="11">
-        <v>5973</v>
-      </c>
-      <c r="N30" s="11">
-        <v>4606</v>
-      </c>
-      <c r="O30" s="11">
-        <v>0</v>
-      </c>
-      <c r="P30" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="11">
-        <v>0</v>
-      </c>
-      <c r="R30" s="11">
-        <v>224206</v>
-      </c>
-      <c r="S30" s="11">
-        <v>9857057</v>
-      </c>
-      <c r="T30" s="20">
-        <v>263.43000000000006</v>
-      </c>
-      <c r="U30" s="12">
-        <v>0.61848099402759782</v>
-      </c>
-      <c r="V30" s="11">
-        <v>32474</v>
-      </c>
-    </row>
-    <row r="31" spans="2:22" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="2:22" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="33" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="1048576" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G1048576" s="3">
+      <c r="B30" s="6">
+        <v>46055</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="7">
+        <v>36</v>
+      </c>
+      <c r="E30" s="7">
+        <v>18</v>
+      </c>
+      <c r="F30" s="7">
+        <v>56</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="H30" s="8">
+        <v>1141931.33</v>
+      </c>
+      <c r="I30" s="8">
+        <v>653129</v>
+      </c>
+      <c r="J30" s="7">
+        <v>22</v>
+      </c>
+      <c r="K30" s="7">
+        <v>18</v>
+      </c>
+      <c r="L30" s="7">
+        <v>306</v>
+      </c>
+      <c r="M30" s="7">
+        <v>177</v>
+      </c>
+      <c r="N30" s="7">
+        <v>131</v>
+      </c>
+      <c r="O30" s="7">
+        <v>3543</v>
+      </c>
+      <c r="P30" s="7">
+        <v>3084</v>
+      </c>
+      <c r="Q30" s="7">
+        <v>1796</v>
+      </c>
+      <c r="R30" s="7">
+        <v>10828</v>
+      </c>
+      <c r="S30" s="7">
+        <v>594404</v>
+      </c>
+      <c r="T30" s="19">
+        <v>10.510000000000002</v>
+      </c>
+      <c r="U30" s="9">
+        <v>1.8216566510319582E-2</v>
+      </c>
+      <c r="V30" s="7">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="6">
+        <v>46056</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="7">
+        <v>45</v>
+      </c>
+      <c r="E31" s="7">
+        <v>20</v>
+      </c>
+      <c r="F31" s="7">
+        <v>69</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0.65217391304347827</v>
+      </c>
+      <c r="H31" s="8">
+        <v>1687196.3</v>
+      </c>
+      <c r="I31" s="8">
+        <v>1141600</v>
+      </c>
+      <c r="J31" s="7">
+        <v>19</v>
+      </c>
+      <c r="K31" s="7">
+        <v>14</v>
+      </c>
+      <c r="L31" s="7">
+        <v>509</v>
+      </c>
+      <c r="M31" s="7">
+        <v>230</v>
+      </c>
+      <c r="N31" s="7">
+        <v>169</v>
+      </c>
+      <c r="O31" s="7">
+        <v>0</v>
+      </c>
+      <c r="P31" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="7">
+        <v>0</v>
+      </c>
+      <c r="R31" s="7">
+        <v>10172</v>
+      </c>
+      <c r="S31" s="7">
+        <v>533625</v>
+      </c>
+      <c r="T31" s="19">
+        <v>11.640000000000002</v>
+      </c>
+      <c r="U31" s="9">
+        <v>1.9062075427500585E-2</v>
+      </c>
+      <c r="V31" s="7">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="6">
+        <v>46057</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="7">
+        <v>326</v>
+      </c>
+      <c r="E32" s="7">
+        <v>97</v>
+      </c>
+      <c r="F32" s="7">
+        <v>400</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="H32" s="8">
+        <v>5324196.9499999983</v>
+      </c>
+      <c r="I32" s="8">
+        <v>4197850</v>
+      </c>
+      <c r="J32" s="7">
+        <v>52</v>
+      </c>
+      <c r="K32" s="7">
+        <v>46</v>
+      </c>
+      <c r="L32" s="7">
+        <v>2576</v>
+      </c>
+      <c r="M32" s="7">
+        <v>225</v>
+      </c>
+      <c r="N32" s="7">
+        <v>171</v>
+      </c>
+      <c r="O32" s="7">
+        <v>0</v>
+      </c>
+      <c r="P32" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="7">
+        <v>0</v>
+      </c>
+      <c r="R32" s="7">
+        <v>9832</v>
+      </c>
+      <c r="S32" s="7">
+        <v>429173</v>
+      </c>
+      <c r="T32" s="19">
+        <v>10.800000000000002</v>
+      </c>
+      <c r="U32" s="9">
+        <v>2.2909176485939237E-2</v>
+      </c>
+      <c r="V32" s="7">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B33" s="6">
+        <v>46058</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="7">
+        <v>65</v>
+      </c>
+      <c r="E33" s="7">
+        <v>26</v>
+      </c>
+      <c r="F33" s="7">
+        <v>102</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0.63725490196078427</v>
+      </c>
+      <c r="H33" s="8">
+        <v>1840398.9</v>
+      </c>
+      <c r="I33" s="8">
+        <v>1185650</v>
+      </c>
+      <c r="J33" s="7">
+        <v>23</v>
+      </c>
+      <c r="K33" s="7">
+        <v>20</v>
+      </c>
+      <c r="L33" s="7">
+        <v>539</v>
+      </c>
+      <c r="M33" s="7">
+        <v>219</v>
+      </c>
+      <c r="N33" s="7">
+        <v>163</v>
+      </c>
+      <c r="O33" s="7">
+        <v>0</v>
+      </c>
+      <c r="P33" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="7">
+        <v>0</v>
+      </c>
+      <c r="R33" s="7">
+        <v>7612</v>
+      </c>
+      <c r="S33" s="7">
+        <v>313945</v>
+      </c>
+      <c r="T33" s="19">
+        <v>10.18</v>
+      </c>
+      <c r="U33" s="9">
+        <v>2.4246285177339979E-2</v>
+      </c>
+      <c r="V33" s="7">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B34" s="6">
+        <v>46059</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="7">
+        <v>166</v>
+      </c>
+      <c r="E34" s="7">
+        <v>45</v>
+      </c>
+      <c r="F34" s="7">
+        <v>245</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0.67755102040816328</v>
+      </c>
+      <c r="H34" s="8">
+        <v>7187272.8099999996</v>
+      </c>
+      <c r="I34" s="8">
+        <v>3413000</v>
+      </c>
+      <c r="J34" s="7">
+        <v>38</v>
+      </c>
+      <c r="K34" s="7">
+        <v>29</v>
+      </c>
+      <c r="L34" s="7">
+        <v>1005</v>
+      </c>
+      <c r="M34" s="7">
+        <v>177</v>
+      </c>
+      <c r="N34" s="7">
+        <v>129</v>
+      </c>
+      <c r="O34" s="7">
+        <v>0</v>
+      </c>
+      <c r="P34" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="7">
+        <v>0</v>
+      </c>
+      <c r="R34" s="7">
+        <v>8050</v>
+      </c>
+      <c r="S34" s="7">
+        <v>311411</v>
+      </c>
+      <c r="T34" s="19">
+        <v>12.540000000000001</v>
+      </c>
+      <c r="U34" s="9">
+        <v>2.5850082367032637E-2</v>
+      </c>
+      <c r="V34" s="7">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B35" s="10">
+        <v>46060</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="11">
+        <v>156</v>
+      </c>
+      <c r="E35" s="11">
+        <v>42</v>
+      </c>
+      <c r="F35" s="11">
+        <v>205</v>
+      </c>
+      <c r="G35" s="12">
+        <v>0.76097560975609757</v>
+      </c>
+      <c r="H35" s="13">
+        <v>8184139.2699999986</v>
+      </c>
+      <c r="I35" s="13">
+        <v>6205100</v>
+      </c>
+      <c r="J35" s="11">
+        <v>23</v>
+      </c>
+      <c r="K35" s="11">
+        <v>21</v>
+      </c>
+      <c r="L35" s="11">
+        <v>1571</v>
+      </c>
+      <c r="M35" s="11">
+        <v>125</v>
+      </c>
+      <c r="N35" s="11">
+        <v>101</v>
+      </c>
+      <c r="O35" s="11">
+        <v>0</v>
+      </c>
+      <c r="P35" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="11">
+        <v>0</v>
+      </c>
+      <c r="R35" s="11">
+        <v>8303</v>
+      </c>
+      <c r="S35" s="11">
+        <v>295942</v>
+      </c>
+      <c r="T35" s="20">
+        <v>12.490000000000002</v>
+      </c>
+      <c r="U35" s="12">
+        <v>2.8056173169066913E-2</v>
+      </c>
+      <c r="V35" s="11">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B36" s="6">
+        <v>46062</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="7">
+        <v>164</v>
+      </c>
+      <c r="E36" s="7">
+        <v>98</v>
+      </c>
+      <c r="F36" s="7">
+        <v>201</v>
+      </c>
+      <c r="G36" s="9">
+        <v>0.8159203980099502</v>
+      </c>
+      <c r="H36" s="8">
+        <v>1739050.7200000002</v>
+      </c>
+      <c r="I36" s="8">
+        <v>1677790</v>
+      </c>
+      <c r="J36" s="7">
+        <v>78</v>
+      </c>
+      <c r="K36" s="7">
+        <v>68</v>
+      </c>
+      <c r="L36" s="7">
+        <v>1190</v>
+      </c>
+      <c r="M36" s="7">
+        <v>213</v>
+      </c>
+      <c r="N36" s="7">
+        <v>153</v>
+      </c>
+      <c r="O36" s="7">
+        <v>0</v>
+      </c>
+      <c r="P36" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="7">
+        <v>0</v>
+      </c>
+      <c r="R36" s="7">
+        <v>9504</v>
+      </c>
+      <c r="S36" s="7">
+        <v>379811</v>
+      </c>
+      <c r="T36" s="19">
+        <v>16.980000000000004</v>
+      </c>
+      <c r="U36" s="9">
+        <v>2.5022971951839203E-2</v>
+      </c>
+      <c r="V36" s="7">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B37" s="6">
+        <v>46063</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" s="7">
+        <v>241</v>
+      </c>
+      <c r="E37" s="7">
+        <v>220</v>
+      </c>
+      <c r="F37" s="7">
+        <v>276</v>
+      </c>
+      <c r="G37" s="9">
+        <v>0.87318840579710144</v>
+      </c>
+      <c r="H37" s="8">
+        <v>1472048.8900000004</v>
+      </c>
+      <c r="I37" s="8">
+        <v>1458480</v>
+      </c>
+      <c r="J37" s="7">
+        <v>75</v>
+      </c>
+      <c r="K37" s="7">
+        <v>72</v>
+      </c>
+      <c r="L37" s="7">
+        <v>1351</v>
+      </c>
+      <c r="M37" s="7">
+        <v>189</v>
+      </c>
+      <c r="N37" s="7">
+        <v>98</v>
+      </c>
+      <c r="O37" s="7">
+        <v>0</v>
+      </c>
+      <c r="P37" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="7">
+        <v>0</v>
+      </c>
+      <c r="R37" s="7">
+        <v>10026</v>
+      </c>
+      <c r="S37" s="7">
+        <v>436167</v>
+      </c>
+      <c r="T37" s="19">
+        <v>18.249999999999993</v>
+      </c>
+      <c r="U37" s="9">
+        <v>2.2986608340383387E-2</v>
+      </c>
+      <c r="V37" s="7">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B38" s="6">
+        <v>46064</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="7">
+        <v>328</v>
+      </c>
+      <c r="E38" s="7">
+        <v>376</v>
+      </c>
+      <c r="F38" s="7">
+        <v>429</v>
+      </c>
+      <c r="G38" s="9">
+        <v>0.76456876456876455</v>
+      </c>
+      <c r="H38" s="8">
+        <v>6804250.0300000012</v>
+      </c>
+      <c r="I38" s="8">
+        <v>2658624</v>
+      </c>
+      <c r="J38" s="7">
+        <v>82</v>
+      </c>
+      <c r="K38" s="7">
+        <v>77</v>
+      </c>
+      <c r="L38" s="7">
+        <v>1926</v>
+      </c>
+      <c r="M38" s="7">
+        <v>213</v>
+      </c>
+      <c r="N38" s="7">
+        <v>156</v>
+      </c>
+      <c r="O38" s="7">
+        <v>0</v>
+      </c>
+      <c r="P38" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="7">
+        <v>0</v>
+      </c>
+      <c r="R38" s="7">
+        <v>9260</v>
+      </c>
+      <c r="S38" s="7">
+        <v>384128</v>
+      </c>
+      <c r="T38" s="19">
+        <v>33.739999999999995</v>
+      </c>
+      <c r="U38" s="9">
+        <v>2.4106547817394203E-2</v>
+      </c>
+      <c r="V38" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B39" s="6">
+        <v>46065</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="7">
+        <v>156</v>
+      </c>
+      <c r="E39" s="7">
+        <v>11</v>
+      </c>
+      <c r="F39" s="7">
+        <v>311</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0.50160771704180063</v>
+      </c>
+      <c r="H39" s="8">
+        <v>5348606.6100000003</v>
+      </c>
+      <c r="I39" s="8">
+        <v>343350</v>
+      </c>
+      <c r="J39" s="7">
+        <v>56</v>
+      </c>
+      <c r="K39" s="7">
+        <v>11</v>
+      </c>
+      <c r="L39" s="7">
+        <v>1375</v>
+      </c>
+      <c r="M39" s="7">
+        <v>113</v>
+      </c>
+      <c r="N39" s="7">
+        <v>87</v>
+      </c>
+      <c r="O39" s="7">
+        <v>0</v>
+      </c>
+      <c r="P39" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="7">
+        <v>0</v>
+      </c>
+      <c r="R39" s="7">
+        <v>0</v>
+      </c>
+      <c r="S39" s="7">
+        <v>0</v>
+      </c>
+      <c r="T39" s="19">
+        <v>0</v>
+      </c>
+      <c r="U39" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V39" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B40" s="6">
+        <v>46066</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7">
+        <v>193</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="8">
+        <v>3304572.5</v>
+      </c>
+      <c r="I40" s="8">
+        <v>0</v>
+      </c>
+      <c r="J40" s="7">
+        <v>12</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L40" s="7">
+        <v>219</v>
+      </c>
+      <c r="M40" s="7">
+        <v>0</v>
+      </c>
+      <c r="N40" s="7">
+        <v>0</v>
+      </c>
+      <c r="O40" s="7">
+        <v>0</v>
+      </c>
+      <c r="P40" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="7">
+        <v>0</v>
+      </c>
+      <c r="R40" s="7">
+        <v>0</v>
+      </c>
+      <c r="S40" s="7">
+        <v>0</v>
+      </c>
+      <c r="T40" s="19">
+        <v>0</v>
+      </c>
+      <c r="U40" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V40" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B41" s="10">
+        <v>46067</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="11">
+        <v>0</v>
+      </c>
+      <c r="E41" s="11">
+        <v>0</v>
+      </c>
+      <c r="F41" s="11">
+        <v>0</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="13">
+        <v>0</v>
+      </c>
+      <c r="I41" s="13">
+        <v>0</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L41" s="11">
+        <v>0</v>
+      </c>
+      <c r="M41" s="11">
+        <v>0</v>
+      </c>
+      <c r="N41" s="11">
+        <v>0</v>
+      </c>
+      <c r="O41" s="11">
+        <v>0</v>
+      </c>
+      <c r="P41" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="11">
+        <v>0</v>
+      </c>
+      <c r="R41" s="11">
+        <v>0</v>
+      </c>
+      <c r="S41" s="11">
+        <v>0</v>
+      </c>
+      <c r="T41" s="20">
+        <v>0</v>
+      </c>
+      <c r="U41" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="V41" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B42" s="6">
+        <v>46069</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="7">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7">
+        <v>0</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="8">
+        <v>0</v>
+      </c>
+      <c r="I42" s="8">
+        <v>0</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L42" s="7">
+        <v>0</v>
+      </c>
+      <c r="M42" s="7">
+        <v>0</v>
+      </c>
+      <c r="N42" s="7">
+        <v>0</v>
+      </c>
+      <c r="O42" s="7">
+        <v>0</v>
+      </c>
+      <c r="P42" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="7">
+        <v>0</v>
+      </c>
+      <c r="R42" s="7">
+        <v>0</v>
+      </c>
+      <c r="S42" s="7">
+        <v>0</v>
+      </c>
+      <c r="T42" s="19">
+        <v>0</v>
+      </c>
+      <c r="U42" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V42" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B43" s="6">
+        <v>46070</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" s="7">
+        <v>0</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0</v>
+      </c>
+      <c r="F43" s="7">
+        <v>0</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="8">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8">
+        <v>0</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43" s="7">
+        <v>0</v>
+      </c>
+      <c r="M43" s="7">
+        <v>0</v>
+      </c>
+      <c r="N43" s="7">
+        <v>0</v>
+      </c>
+      <c r="O43" s="7">
+        <v>0</v>
+      </c>
+      <c r="P43" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="7">
+        <v>0</v>
+      </c>
+      <c r="R43" s="7">
+        <v>0</v>
+      </c>
+      <c r="S43" s="7">
+        <v>0</v>
+      </c>
+      <c r="T43" s="19">
+        <v>0</v>
+      </c>
+      <c r="U43" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V43" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B44" s="6">
+        <v>46071</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="7">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7">
+        <v>0</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="8">
+        <v>0</v>
+      </c>
+      <c r="I44" s="8">
+        <v>0</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L44" s="7">
+        <v>0</v>
+      </c>
+      <c r="M44" s="7">
+        <v>0</v>
+      </c>
+      <c r="N44" s="7">
+        <v>0</v>
+      </c>
+      <c r="O44" s="7">
+        <v>0</v>
+      </c>
+      <c r="P44" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="7">
+        <v>0</v>
+      </c>
+      <c r="R44" s="7">
+        <v>0</v>
+      </c>
+      <c r="S44" s="7">
+        <v>0</v>
+      </c>
+      <c r="T44" s="19">
+        <v>0</v>
+      </c>
+      <c r="U44" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V44" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B45" s="6">
+        <v>46072</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="7">
+        <v>0</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0</v>
+      </c>
+      <c r="F45" s="7">
+        <v>69</v>
+      </c>
+      <c r="G45" s="9">
+        <v>0</v>
+      </c>
+      <c r="H45" s="8">
+        <v>519281.27</v>
+      </c>
+      <c r="I45" s="8">
+        <v>0</v>
+      </c>
+      <c r="J45" s="7">
+        <v>3</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L45" s="7">
+        <v>69</v>
+      </c>
+      <c r="M45" s="7">
+        <v>0</v>
+      </c>
+      <c r="N45" s="7">
+        <v>0</v>
+      </c>
+      <c r="O45" s="7">
+        <v>0</v>
+      </c>
+      <c r="P45" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="7">
+        <v>0</v>
+      </c>
+      <c r="R45" s="7">
+        <v>0</v>
+      </c>
+      <c r="S45" s="7">
+        <v>0</v>
+      </c>
+      <c r="T45" s="19">
+        <v>0</v>
+      </c>
+      <c r="U45" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V45" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B46" s="6">
+        <v>46073</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7">
+        <v>235</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="8">
+        <v>230190</v>
+      </c>
+      <c r="I46" s="8">
+        <v>0</v>
+      </c>
+      <c r="J46" s="7">
+        <v>7</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L46" s="7">
+        <v>233</v>
+      </c>
+      <c r="M46" s="7">
+        <v>0</v>
+      </c>
+      <c r="N46" s="7">
+        <v>0</v>
+      </c>
+      <c r="O46" s="7">
+        <v>0</v>
+      </c>
+      <c r="P46" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="7">
+        <v>0</v>
+      </c>
+      <c r="R46" s="7">
+        <v>0</v>
+      </c>
+      <c r="S46" s="7">
+        <v>0</v>
+      </c>
+      <c r="T46" s="19">
+        <v>0</v>
+      </c>
+      <c r="U46" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V46" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B47" s="10">
+        <v>46074</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="11">
+        <v>0</v>
+      </c>
+      <c r="E47" s="11">
+        <v>0</v>
+      </c>
+      <c r="F47" s="11">
+        <v>19</v>
+      </c>
+      <c r="G47" s="12">
+        <v>0</v>
+      </c>
+      <c r="H47" s="13">
+        <v>64380</v>
+      </c>
+      <c r="I47" s="13">
+        <v>0</v>
+      </c>
+      <c r="J47" s="11">
+        <v>2</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47" s="11">
+        <v>33</v>
+      </c>
+      <c r="M47" s="11">
+        <v>0</v>
+      </c>
+      <c r="N47" s="11">
+        <v>0</v>
+      </c>
+      <c r="O47" s="11">
+        <v>0</v>
+      </c>
+      <c r="P47" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="11">
+        <v>0</v>
+      </c>
+      <c r="R47" s="11">
+        <v>0</v>
+      </c>
+      <c r="S47" s="11">
+        <v>0</v>
+      </c>
+      <c r="T47" s="20">
+        <v>0</v>
+      </c>
+      <c r="U47" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="V47" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B48" s="6">
+        <v>46076</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="7">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7">
+        <v>14</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0</v>
+      </c>
+      <c r="H48" s="8">
+        <v>21800</v>
+      </c>
+      <c r="I48" s="8">
+        <v>0</v>
+      </c>
+      <c r="J48" s="7">
+        <v>9</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L48" s="7">
+        <v>63</v>
+      </c>
+      <c r="M48" s="7">
+        <v>0</v>
+      </c>
+      <c r="N48" s="7">
+        <v>0</v>
+      </c>
+      <c r="O48" s="7">
+        <v>0</v>
+      </c>
+      <c r="P48" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="7">
+        <v>0</v>
+      </c>
+      <c r="R48" s="7">
+        <v>0</v>
+      </c>
+      <c r="S48" s="7">
+        <v>0</v>
+      </c>
+      <c r="T48" s="19">
+        <v>0</v>
+      </c>
+      <c r="U48" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V48" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B49" s="6">
+        <v>46077</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" s="7">
+        <v>0</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0</v>
+      </c>
+      <c r="F49" s="7">
+        <v>270</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0</v>
+      </c>
+      <c r="H49" s="8">
+        <v>614680</v>
+      </c>
+      <c r="I49" s="8">
+        <v>0</v>
+      </c>
+      <c r="J49" s="7">
+        <v>7</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49" s="7">
+        <v>338</v>
+      </c>
+      <c r="M49" s="7">
+        <v>0</v>
+      </c>
+      <c r="N49" s="7">
+        <v>0</v>
+      </c>
+      <c r="O49" s="7">
+        <v>0</v>
+      </c>
+      <c r="P49" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="7">
+        <v>0</v>
+      </c>
+      <c r="R49" s="7">
+        <v>0</v>
+      </c>
+      <c r="S49" s="7">
+        <v>0</v>
+      </c>
+      <c r="T49" s="19">
+        <v>0</v>
+      </c>
+      <c r="U49" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V49" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B50" s="6">
+        <v>46078</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" s="7">
+        <v>0</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7">
+        <v>200</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="8">
+        <v>98472</v>
+      </c>
+      <c r="I50" s="8">
+        <v>0</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L50" s="7">
+        <v>8</v>
+      </c>
+      <c r="M50" s="7">
+        <v>0</v>
+      </c>
+      <c r="N50" s="7">
+        <v>0</v>
+      </c>
+      <c r="O50" s="7">
+        <v>0</v>
+      </c>
+      <c r="P50" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="7">
+        <v>0</v>
+      </c>
+      <c r="R50" s="7">
+        <v>0</v>
+      </c>
+      <c r="S50" s="7">
+        <v>0</v>
+      </c>
+      <c r="T50" s="19">
+        <v>0</v>
+      </c>
+      <c r="U50" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V50" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B51" s="6">
+        <v>46079</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" s="7">
+        <v>0</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0</v>
+      </c>
+      <c r="F51" s="7">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" s="8">
+        <v>0</v>
+      </c>
+      <c r="I51" s="8">
+        <v>0</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L51" s="7">
+        <v>0</v>
+      </c>
+      <c r="M51" s="7">
+        <v>0</v>
+      </c>
+      <c r="N51" s="7">
+        <v>0</v>
+      </c>
+      <c r="O51" s="7">
+        <v>0</v>
+      </c>
+      <c r="P51" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="7">
+        <v>0</v>
+      </c>
+      <c r="R51" s="7">
+        <v>0</v>
+      </c>
+      <c r="S51" s="7">
+        <v>0</v>
+      </c>
+      <c r="T51" s="19">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V51" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B52" s="6">
+        <v>46080</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" s="7">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7">
+        <v>81</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="8">
+        <v>865800</v>
+      </c>
+      <c r="I52" s="8">
+        <v>0</v>
+      </c>
+      <c r="J52" s="7">
+        <v>5</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L52" s="7">
+        <v>109</v>
+      </c>
+      <c r="M52" s="7">
+        <v>0</v>
+      </c>
+      <c r="N52" s="7">
+        <v>0</v>
+      </c>
+      <c r="O52" s="7">
+        <v>0</v>
+      </c>
+      <c r="P52" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="7">
+        <v>0</v>
+      </c>
+      <c r="R52" s="7">
+        <v>0</v>
+      </c>
+      <c r="S52" s="7">
+        <v>0</v>
+      </c>
+      <c r="T52" s="19">
+        <v>0</v>
+      </c>
+      <c r="U52" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V52" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B53" s="10">
+        <v>46081</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" s="11">
+        <v>0</v>
+      </c>
+      <c r="E53" s="11">
+        <v>0</v>
+      </c>
+      <c r="F53" s="11">
+        <v>70</v>
+      </c>
+      <c r="G53" s="12">
+        <v>0</v>
+      </c>
+      <c r="H53" s="13">
+        <v>155900</v>
+      </c>
+      <c r="I53" s="13">
+        <v>0</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L53" s="11">
+        <v>6</v>
+      </c>
+      <c r="M53" s="11">
+        <v>0</v>
+      </c>
+      <c r="N53" s="11">
+        <v>0</v>
+      </c>
+      <c r="O53" s="11">
+        <v>0</v>
+      </c>
+      <c r="P53" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="11">
+        <v>0</v>
+      </c>
+      <c r="R53" s="11">
+        <v>0</v>
+      </c>
+      <c r="S53" s="11">
+        <v>0</v>
+      </c>
+      <c r="T53" s="20">
+        <v>0</v>
+      </c>
+      <c r="U53" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="V53" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1048575" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G1048575" s="3">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="B1:M1"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="R1:U1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G35:G1048576 G3:G30">
-    <cfRule type="dataBar" priority="4">
+  <conditionalFormatting sqref="G54:G1048576">
+    <cfRule type="dataBar" priority="6">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7830,6 +12196,20 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{DA2B1F3A-80C0-492A-AF5E-1C91EB6420F3}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G53">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D10A7880-4FCE-4F0C-AD89-F35966962522}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7854,7 +12234,20 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G35:G1048576 G3:G30</xm:sqref>
+          <xm:sqref>G54:G1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D10A7880-4FCE-4F0C-AD89-F35966962522}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G3:G53</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
